--- a/resources/pet/pet.xlsx
+++ b/resources/pet/pet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="灵兽表说明" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="灵兽表说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pet" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="2">Pet!#REF!</definedName>
@@ -7892,52 +7892,80 @@
       <c r="AT52" s="43" t="n"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="27" t="n"/>
-      <c r="B53" s="28" t="n"/>
-      <c r="C53" s="28" t="n"/>
-      <c r="D53" s="27" t="n"/>
-      <c r="E53" s="27" t="n"/>
+      <c r="A53" s="43" t="n">
+        <v>8891</v>
+      </c>
+      <c r="B53" s="44" t="n"/>
+      <c r="C53" s="44" t="inlineStr">
+        <is>
+          <t>九尾天狐</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="n">
+        <v>1070</v>
+      </c>
+      <c r="E53" s="43" t="n"/>
       <c r="F53" s="22" t="n"/>
       <c r="G53" s="22" t="n"/>
-      <c r="H53" s="27" t="n"/>
-      <c r="I53" s="27" t="n"/>
-      <c r="J53" s="28" t="n"/>
-      <c r="K53" s="27" t="n"/>
-      <c r="L53" s="27" t="n"/>
-      <c r="M53" s="27" t="n"/>
-      <c r="N53" s="27" t="n"/>
-      <c r="O53" s="30" t="n"/>
-      <c r="P53" s="30" t="n"/>
-      <c r="Q53" s="30" t="n"/>
-      <c r="R53" s="30" t="n"/>
-      <c r="S53" s="30" t="n"/>
-      <c r="T53" s="30" t="n"/>
-      <c r="U53" s="27" t="n"/>
-      <c r="V53" s="27" t="n"/>
-      <c r="W53" s="27" t="n"/>
-      <c r="X53" s="27" t="n"/>
-      <c r="Y53" s="27" t="n"/>
-      <c r="Z53" s="27" t="n"/>
-      <c r="AA53" s="27" t="n"/>
-      <c r="AB53" s="27" t="n"/>
-      <c r="AC53" s="27" t="n"/>
-      <c r="AD53" s="27" t="n"/>
-      <c r="AE53" s="28" t="n"/>
-      <c r="AF53" s="28" t="n"/>
-      <c r="AG53" s="28" t="n"/>
-      <c r="AH53" s="28" t="n"/>
-      <c r="AI53" s="27" t="n"/>
-      <c r="AJ53" s="27" t="n"/>
-      <c r="AK53" s="30" t="n"/>
-      <c r="AL53" s="27" t="n"/>
-      <c r="AM53" s="27" t="n"/>
-      <c r="AN53" s="27" t="n"/>
-      <c r="AO53" s="27" t="n"/>
-      <c r="AP53" s="27" t="n"/>
-      <c r="AQ53" s="27" t="n"/>
-      <c r="AR53" s="27" t="n"/>
-      <c r="AS53" s="27" t="n"/>
-      <c r="AT53" s="27" t="n"/>
+      <c r="H53" s="43" t="n"/>
+      <c r="I53" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="44" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="K53" s="43" t="n">
+        <v>28999</v>
+      </c>
+      <c r="L53" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="M53" s="43" t="n"/>
+      <c r="N53" s="43" t="n">
+        <v>6000</v>
+      </c>
+      <c r="O53" s="45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P53" s="45" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q53" s="45" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R53" s="45" t="n">
+        <v>1500</v>
+      </c>
+      <c r="S53" s="45" t="n"/>
+      <c r="T53" s="45" t="n"/>
+      <c r="U53" s="43" t="n"/>
+      <c r="V53" s="43" t="n"/>
+      <c r="W53" s="43" t="n"/>
+      <c r="X53" s="43" t="n"/>
+      <c r="Y53" s="43" t="n"/>
+      <c r="Z53" s="43" t="n"/>
+      <c r="AA53" s="43" t="n"/>
+      <c r="AB53" s="43" t="n"/>
+      <c r="AC53" s="43" t="n"/>
+      <c r="AD53" s="43" t="n"/>
+      <c r="AE53" s="44" t="n"/>
+      <c r="AF53" s="44" t="n"/>
+      <c r="AG53" s="44" t="n"/>
+      <c r="AH53" s="44" t="n"/>
+      <c r="AI53" s="43" t="n"/>
+      <c r="AJ53" s="43" t="n"/>
+      <c r="AK53" s="45" t="n"/>
+      <c r="AL53" s="43" t="n"/>
+      <c r="AM53" s="43" t="n"/>
+      <c r="AN53" s="43" t="n"/>
+      <c r="AO53" s="43" t="n"/>
+      <c r="AP53" s="43" t="n"/>
+      <c r="AQ53" s="43" t="n"/>
+      <c r="AR53" s="43" t="n"/>
+      <c r="AS53" s="43" t="n"/>
+      <c r="AT53" s="43" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
       <c r="A54" s="27" t="n"/>

--- a/resources/pet/pet.xlsx
+++ b/resources/pet/pet.xlsx
@@ -7968,100 +7968,152 @@
       <c r="AT53" s="43" t="n"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="27" t="n"/>
-      <c r="B54" s="28" t="n"/>
-      <c r="C54" s="28" t="n"/>
-      <c r="D54" s="27" t="n"/>
-      <c r="E54" s="27" t="n"/>
+      <c r="A54" s="43" t="n">
+        <v>8892</v>
+      </c>
+      <c r="B54" s="44" t="n"/>
+      <c r="C54" s="44" t="inlineStr">
+        <is>
+          <t>焚天朱雀</t>
+        </is>
+      </c>
+      <c r="D54" s="43" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E54" s="43" t="n"/>
       <c r="F54" s="22" t="n"/>
       <c r="G54" s="22" t="n"/>
-      <c r="H54" s="27" t="n"/>
-      <c r="I54" s="27" t="n"/>
-      <c r="J54" s="28" t="n"/>
-      <c r="K54" s="27" t="n"/>
-      <c r="L54" s="27" t="n"/>
-      <c r="M54" s="27" t="n"/>
-      <c r="N54" s="27" t="n"/>
-      <c r="O54" s="30" t="n"/>
-      <c r="P54" s="30" t="n"/>
-      <c r="Q54" s="30" t="n"/>
-      <c r="R54" s="30" t="n"/>
-      <c r="S54" s="30" t="n"/>
-      <c r="T54" s="30" t="n"/>
-      <c r="U54" s="27" t="n"/>
-      <c r="V54" s="27" t="n"/>
-      <c r="W54" s="27" t="n"/>
-      <c r="X54" s="27" t="n"/>
-      <c r="Y54" s="27" t="n"/>
-      <c r="Z54" s="27" t="n"/>
-      <c r="AA54" s="27" t="n"/>
-      <c r="AB54" s="27" t="n"/>
-      <c r="AC54" s="27" t="n"/>
-      <c r="AD54" s="27" t="n"/>
-      <c r="AE54" s="28" t="n"/>
-      <c r="AF54" s="28" t="n"/>
-      <c r="AG54" s="28" t="n"/>
-      <c r="AH54" s="28" t="n"/>
-      <c r="AI54" s="27" t="n"/>
-      <c r="AJ54" s="27" t="n"/>
-      <c r="AK54" s="30" t="n"/>
-      <c r="AL54" s="27" t="n"/>
-      <c r="AM54" s="27" t="n"/>
-      <c r="AN54" s="27" t="n"/>
-      <c r="AO54" s="27" t="n"/>
-      <c r="AP54" s="27" t="n"/>
-      <c r="AQ54" s="27" t="n"/>
-      <c r="AR54" s="27" t="n"/>
-      <c r="AS54" s="27" t="n"/>
-      <c r="AT54" s="27" t="n"/>
+      <c r="H54" s="43" t="n"/>
+      <c r="I54" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="44" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="K54" s="43" t="n">
+        <v>8892</v>
+      </c>
+      <c r="L54" s="43" t="n"/>
+      <c r="M54" s="43" t="n"/>
+      <c r="N54" s="43" t="n">
+        <v>6500</v>
+      </c>
+      <c r="O54" s="45" t="n"/>
+      <c r="P54" s="45" t="n"/>
+      <c r="Q54" s="45" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R54" s="45" t="n"/>
+      <c r="S54" s="45" t="n"/>
+      <c r="T54" s="45" t="n"/>
+      <c r="U54" s="43" t="n"/>
+      <c r="V54" s="43" t="n"/>
+      <c r="W54" s="43" t="n"/>
+      <c r="X54" s="43" t="n"/>
+      <c r="Y54" s="43" t="n"/>
+      <c r="Z54" s="43" t="n"/>
+      <c r="AA54" s="43" t="n"/>
+      <c r="AB54" s="43" t="n"/>
+      <c r="AC54" s="43" t="n"/>
+      <c r="AD54" s="43" t="n"/>
+      <c r="AE54" s="44" t="n"/>
+      <c r="AF54" s="44" t="n"/>
+      <c r="AG54" s="44" t="n"/>
+      <c r="AH54" s="44" t="n"/>
+      <c r="AI54" s="43" t="n"/>
+      <c r="AJ54" s="43" t="n"/>
+      <c r="AK54" s="45" t="n"/>
+      <c r="AL54" s="43" t="n"/>
+      <c r="AM54" s="43" t="n"/>
+      <c r="AN54" s="43" t="n"/>
+      <c r="AO54" s="43" t="n"/>
+      <c r="AP54" s="43" t="n"/>
+      <c r="AQ54" s="43" t="n"/>
+      <c r="AR54" s="43" t="n"/>
+      <c r="AS54" s="43" t="n"/>
+      <c r="AT54" s="43" t="n"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="27" t="n"/>
-      <c r="B55" s="28" t="n"/>
-      <c r="C55" s="28" t="n"/>
-      <c r="D55" s="27" t="n"/>
-      <c r="E55" s="27" t="n"/>
+      <c r="A55" s="43" t="n">
+        <v>8893</v>
+      </c>
+      <c r="B55" s="44" t="n"/>
+      <c r="C55" s="44" t="inlineStr">
+        <is>
+          <t>焚天朱雀</t>
+        </is>
+      </c>
+      <c r="D55" s="43" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E55" s="43" t="n"/>
       <c r="F55" s="22" t="n"/>
       <c r="G55" s="22" t="n"/>
-      <c r="H55" s="27" t="n"/>
-      <c r="I55" s="27" t="n"/>
-      <c r="J55" s="28" t="n"/>
-      <c r="K55" s="27" t="n"/>
-      <c r="L55" s="27" t="n"/>
-      <c r="M55" s="27" t="n"/>
-      <c r="N55" s="27" t="n"/>
-      <c r="O55" s="30" t="n"/>
-      <c r="P55" s="30" t="n"/>
-      <c r="Q55" s="30" t="n"/>
-      <c r="R55" s="30" t="n"/>
-      <c r="S55" s="30" t="n"/>
-      <c r="T55" s="30" t="n"/>
-      <c r="U55" s="27" t="n"/>
-      <c r="V55" s="27" t="n"/>
-      <c r="W55" s="27" t="n"/>
-      <c r="X55" s="27" t="n"/>
-      <c r="Y55" s="27" t="n"/>
-      <c r="Z55" s="27" t="n"/>
-      <c r="AA55" s="27" t="n"/>
-      <c r="AB55" s="27" t="n"/>
-      <c r="AC55" s="27" t="n"/>
-      <c r="AD55" s="27" t="n"/>
-      <c r="AE55" s="28" t="n"/>
-      <c r="AF55" s="28" t="n"/>
-      <c r="AG55" s="28" t="n"/>
-      <c r="AH55" s="28" t="n"/>
-      <c r="AI55" s="27" t="n"/>
-      <c r="AJ55" s="27" t="n"/>
-      <c r="AK55" s="30" t="n"/>
-      <c r="AL55" s="27" t="n"/>
-      <c r="AM55" s="27" t="n"/>
-      <c r="AN55" s="27" t="n"/>
-      <c r="AO55" s="27" t="n"/>
-      <c r="AP55" s="27" t="n"/>
-      <c r="AQ55" s="27" t="n"/>
-      <c r="AR55" s="27" t="n"/>
-      <c r="AS55" s="27" t="n"/>
-      <c r="AT55" s="27" t="n"/>
+      <c r="H55" s="43" t="n"/>
+      <c r="I55" s="43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" s="44" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="K55" s="43" t="n">
+        <v>8893</v>
+      </c>
+      <c r="L55" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="M55" s="43" t="n">
+        <v>2</v>
+      </c>
+      <c r="N55" s="43" t="n">
+        <v>6500</v>
+      </c>
+      <c r="O55" s="45" t="n">
+        <v>1800</v>
+      </c>
+      <c r="P55" s="45" t="n">
+        <v>3200</v>
+      </c>
+      <c r="Q55" s="45" t="n">
+        <v>1400</v>
+      </c>
+      <c r="R55" s="45" t="n">
+        <v>1400</v>
+      </c>
+      <c r="S55" s="45" t="n"/>
+      <c r="T55" s="45" t="n"/>
+      <c r="U55" s="43" t="n">
+        <v>900015</v>
+      </c>
+      <c r="V55" s="43" t="n"/>
+      <c r="W55" s="43" t="n"/>
+      <c r="X55" s="43" t="n"/>
+      <c r="Y55" s="43" t="n"/>
+      <c r="Z55" s="43" t="n"/>
+      <c r="AA55" s="43" t="n"/>
+      <c r="AB55" s="43" t="n"/>
+      <c r="AC55" s="43" t="n"/>
+      <c r="AD55" s="43" t="n"/>
+      <c r="AE55" s="44" t="n"/>
+      <c r="AF55" s="44" t="n"/>
+      <c r="AG55" s="44" t="n"/>
+      <c r="AH55" s="44" t="n"/>
+      <c r="AI55" s="43" t="n"/>
+      <c r="AJ55" s="43" t="n"/>
+      <c r="AK55" s="45" t="n"/>
+      <c r="AL55" s="43" t="n"/>
+      <c r="AM55" s="43" t="n"/>
+      <c r="AN55" s="43" t="n"/>
+      <c r="AO55" s="43" t="n"/>
+      <c r="AP55" s="43" t="n"/>
+      <c r="AQ55" s="43" t="n"/>
+      <c r="AR55" s="43" t="n"/>
+      <c r="AS55" s="43" t="n"/>
+      <c r="AT55" s="43" t="n"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
       <c r="A56" s="27" t="n"/>

--- a/resources/pet/pet.xlsx
+++ b/resources/pet/pet.xlsx
@@ -452,7 +452,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -548,6 +548,39 @@
     </xf>
     <xf numFmtId="3" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -1082,7 +1115,7 @@
           <t>生成文件</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
@@ -1100,7 +1133,7 @@
       <c r="E4" s="0" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
@@ -1154,7 +1187,7 @@
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" s="8">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>配置数字</t>
         </is>
@@ -1678,157 +1711,297 @@
       </c>
     </row>
     <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="19" t="n"/>
-      <c r="B3" s="19" t="n"/>
-      <c r="C3" s="19" t="n"/>
-      <c r="D3" s="19" t="n"/>
-      <c r="E3" s="19" t="n"/>
-      <c r="F3" s="20" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="19" t="n"/>
-      <c r="I3" s="19" t="n"/>
-      <c r="J3" s="19" t="n"/>
-      <c r="K3" s="19" t="n"/>
-      <c r="L3" s="19" t="n"/>
-      <c r="M3" s="19" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="N3" s="19" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="O3" s="19" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="P3" s="19" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="Q3" s="19" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="R3" s="19" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="S3" s="19" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="T3" s="19" t="n"/>
-      <c r="U3" s="21" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="V3" s="21" t="n"/>
-      <c r="W3" s="21" t="n"/>
-      <c r="X3" s="21" t="n"/>
-      <c r="Y3" s="21" t="n"/>
-      <c r="Z3" s="21" t="n"/>
-      <c r="AA3" s="21" t="n"/>
-      <c r="AB3" s="21" t="n"/>
-      <c r="AC3" s="21" t="n"/>
-      <c r="AD3" s="21" t="n"/>
-      <c r="AE3" s="21" t="n"/>
-      <c r="AF3" s="21" t="n"/>
-      <c r="AG3" s="21" t="n"/>
-      <c r="AH3" s="21" t="n"/>
-      <c r="AI3" s="19" t="n"/>
-      <c r="AJ3" s="19" t="n"/>
-      <c r="AK3" s="19" t="n"/>
-      <c r="AL3" s="19" t="n"/>
-      <c r="AM3" s="19" t="n"/>
-      <c r="AN3" s="19" t="n"/>
-      <c r="AO3" s="19" t="n"/>
-      <c r="AP3" s="19" t="n"/>
-      <c r="AQ3" s="21" t="n"/>
-      <c r="AR3" s="21" t="n"/>
-      <c r="AS3" s="21" t="n"/>
-      <c r="AT3" s="21" t="n"/>
+      <c r="A3" s="34" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B3" s="35" t="n"/>
+      <c r="C3" s="36" t="inlineStr">
+        <is>
+          <t>火焰犬</t>
+        </is>
+      </c>
+      <c r="D3" s="37" t="n">
+        <v>1052</v>
+      </c>
+      <c r="E3" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="38" t="n"/>
+      <c r="G3" s="38" t="n"/>
+      <c r="H3" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J3" s="35" t="n"/>
+      <c r="K3" s="35" t="n"/>
+      <c r="L3" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="39" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="O3" s="39" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="P3" s="39" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="Q3" s="39" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R3" s="39" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S3" s="39" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="T3" s="39" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="U3" s="39" t="n">
+        <v>8001</v>
+      </c>
+      <c r="V3" s="39" t="n">
+        <v>6556</v>
+      </c>
+      <c r="W3" s="39" t="n">
+        <v>5005</v>
+      </c>
+      <c r="X3" s="39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Y3" s="39" t="n">
+        <v>6011</v>
+      </c>
+      <c r="Z3" s="39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AA3" s="39" t="n">
+        <v>5040</v>
+      </c>
+      <c r="AB3" s="39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AC3" s="39" t="n">
+        <v>5046</v>
+      </c>
+      <c r="AD3" s="39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AE3" s="40" t="n"/>
+      <c r="AF3" s="40" t="n"/>
+      <c r="AG3" s="40" t="n"/>
+      <c r="AH3" s="40" t="n"/>
+      <c r="AI3" s="39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" s="39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" s="39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AL3" s="39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" s="39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP3" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ3" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR3" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="39" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="19" t="n"/>
-      <c r="B4" s="19" t="n"/>
-      <c r="C4" s="19" t="n"/>
-      <c r="D4" s="19" t="n"/>
-      <c r="E4" s="19" t="n"/>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>pet_icon_default.png</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>big_img_pet_default.png</t>
-        </is>
-      </c>
-      <c r="H4" s="19" t="n"/>
-      <c r="I4" s="19" t="n"/>
-      <c r="J4" s="19" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K4" s="19" t="n"/>
-      <c r="L4" s="19" t="n"/>
-      <c r="M4" s="19" t="n"/>
-      <c r="N4" s="22" t="n"/>
-      <c r="O4" s="22" t="n"/>
-      <c r="P4" s="22" t="n"/>
-      <c r="Q4" s="22" t="n"/>
-      <c r="R4" s="22" t="n"/>
-      <c r="S4" s="22" t="n"/>
-      <c r="T4" s="22" t="n"/>
-      <c r="U4" s="19" t="n"/>
-      <c r="V4" s="21" t="n"/>
-      <c r="W4" s="21" t="n"/>
-      <c r="X4" s="21" t="n"/>
-      <c r="Y4" s="21" t="n"/>
-      <c r="Z4" s="21" t="n"/>
-      <c r="AA4" s="21" t="n"/>
-      <c r="AB4" s="21" t="n"/>
-      <c r="AC4" s="21" t="n"/>
-      <c r="AD4" s="21" t="n"/>
-      <c r="AE4" s="21" t="n"/>
-      <c r="AF4" s="21" t="n"/>
-      <c r="AG4" s="21" t="n"/>
-      <c r="AH4" s="21" t="n"/>
-      <c r="AI4" s="22" t="n"/>
-      <c r="AJ4" s="22" t="n"/>
-      <c r="AK4" s="22" t="n"/>
-      <c r="AL4" s="22" t="n"/>
-      <c r="AM4" s="22" t="n"/>
-      <c r="AN4" s="22" t="n"/>
-      <c r="AO4" s="22" t="n"/>
-      <c r="AP4" s="22" t="n"/>
-      <c r="AQ4" s="19" t="n"/>
-      <c r="AR4" s="21" t="n"/>
-      <c r="AS4" s="21" t="n"/>
-      <c r="AT4" s="21" t="n"/>
+      <c r="A4" s="34" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B4" s="35" t="n"/>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>小白鲸</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E4" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n"/>
+      <c r="H4" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="35" t="n"/>
+      <c r="K4" s="35" t="n"/>
+      <c r="L4" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="38" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="39" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="O4" s="39" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="P4" s="39" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q4" s="39" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R4" s="39" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S4" s="39" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="T4" s="39" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="U4" s="39" t="n">
+        <v>8004</v>
+      </c>
+      <c r="V4" s="39" t="n">
+        <v>5503</v>
+      </c>
+      <c r="W4" s="39" t="n">
+        <v>6553</v>
+      </c>
+      <c r="X4" s="39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Y4" s="39" t="n">
+        <v>5029</v>
+      </c>
+      <c r="Z4" s="39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AA4" s="39" t="n">
+        <v>5034</v>
+      </c>
+      <c r="AB4" s="39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AC4" s="39" t="n">
+        <v>6013</v>
+      </c>
+      <c r="AD4" s="39" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AE4" s="40" t="n"/>
+      <c r="AF4" s="40" t="n"/>
+      <c r="AG4" s="40" t="n"/>
+      <c r="AH4" s="40" t="n"/>
+      <c r="AI4" s="39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" s="39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" s="39" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AL4" s="39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" s="39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" s="39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO4" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP4" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ4" s="39" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR4" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" s="39" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="5" customFormat="1" s="30">
       <c r="A5" s="23" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B5" s="24" t="n"/>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>火焰犬</t>
+          <t>木结花</t>
         </is>
       </c>
       <c r="D5" s="26" t="n">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="E5" s="26" t="n">
         <v>0</v>
@@ -1847,16 +2020,16 @@
         <v>1</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5" s="28" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="O5" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P5" s="28" t="inlineStr">
@@ -1876,7 +2049,7 @@
       </c>
       <c r="S5" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T5" s="28" t="inlineStr">
@@ -1885,31 +2058,31 @@
         </is>
       </c>
       <c r="U5" s="28" t="n">
-        <v>8001</v>
+        <v>8007</v>
       </c>
       <c r="V5" s="28" t="n">
-        <v>6556</v>
+        <v>5047</v>
       </c>
       <c r="W5" s="28" t="n">
-        <v>5005</v>
+        <v>5022</v>
       </c>
       <c r="X5" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y5" s="28" t="n">
-        <v>6011</v>
+        <v>5028</v>
       </c>
       <c r="Z5" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA5" s="28" t="n">
-        <v>5040</v>
+        <v>5042</v>
       </c>
       <c r="AB5" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC5" s="28" t="n">
-        <v>5046</v>
+        <v>5026</v>
       </c>
       <c r="AD5" s="28" t="n">
         <v>2500</v>
@@ -1959,19 +2132,19 @@
     </row>
     <row r="6" customFormat="1" s="30">
       <c r="A6" s="23" t="n">
-        <v>2052</v>
+        <v>1055</v>
       </c>
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>烈焰犬</t>
+          <t>小顽蝠</t>
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="27" t="n"/>
       <c r="G6" s="27" t="n"/>
@@ -1987,69 +2160,69 @@
         <v>1</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="28" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="O6" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P6" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="Q6" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="R6" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S6" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T6" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U6" s="28" t="n">
-        <v>8002</v>
+        <v>8010</v>
       </c>
       <c r="V6" s="28" t="n">
-        <v>6556</v>
+        <v>5010</v>
       </c>
       <c r="W6" s="28" t="n">
-        <v>5005</v>
+        <v>6554</v>
       </c>
       <c r="X6" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y6" s="28" t="n">
-        <v>6011</v>
+        <v>5037</v>
       </c>
       <c r="Z6" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA6" s="28" t="n">
-        <v>5040</v>
+        <v>5038</v>
       </c>
       <c r="AB6" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC6" s="28" t="n">
-        <v>5046</v>
+        <v>5057</v>
       </c>
       <c r="AD6" s="28" t="n">
         <v>2500</v>
@@ -2099,19 +2272,19 @@
     </row>
     <row r="7" customFormat="1" s="30">
       <c r="A7" s="23" t="n">
-        <v>3052</v>
+        <v>1056</v>
       </c>
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>炽焰獒</t>
+          <t>慢慢龟</t>
         </is>
       </c>
       <c r="D7" s="26" t="n">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="27" t="n"/>
       <c r="G7" s="27" t="n"/>
@@ -2127,21 +2300,21 @@
         <v>1</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N7" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="O7" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P7" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="Q7" s="28" t="inlineStr">
@@ -2151,45 +2324,45 @@
       </c>
       <c r="R7" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S7" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T7" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U7" s="28" t="n">
-        <v>8003</v>
+        <v>8013</v>
       </c>
       <c r="V7" s="28" t="n">
-        <v>6556</v>
+        <v>5503</v>
       </c>
       <c r="W7" s="28" t="n">
-        <v>5005</v>
+        <v>5025</v>
       </c>
       <c r="X7" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="Z7" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>5040</v>
+        <v>5009</v>
       </c>
       <c r="AB7" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC7" s="28" t="n">
-        <v>5046</v>
+        <v>6029</v>
       </c>
       <c r="AD7" s="28" t="n">
         <v>2500</v>
@@ -2238,17 +2411,17 @@
       </c>
     </row>
     <row r="8" customFormat="1" s="30">
-      <c r="A8" s="23" t="n">
-        <v>1053</v>
+      <c r="A8" s="31" t="n">
+        <v>1057</v>
       </c>
       <c r="B8" s="24" t="n"/>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>小白鲸</t>
+          <t>岩岩石</t>
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>0</v>
@@ -2267,36 +2440,36 @@
         <v>1</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" s="28" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="O8" s="28" t="inlineStr">
         <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="P8" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P8" s="28" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
       <c r="Q8" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="R8" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S8" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T8" s="28" t="inlineStr">
@@ -2305,31 +2478,31 @@
         </is>
       </c>
       <c r="U8" s="28" t="n">
-        <v>8004</v>
+        <v>8016</v>
       </c>
       <c r="V8" s="28" t="n">
-        <v>5503</v>
+        <v>6022</v>
       </c>
       <c r="W8" s="28" t="n">
-        <v>6553</v>
+        <v>5021</v>
       </c>
       <c r="X8" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y8" s="28" t="n">
-        <v>5029</v>
+        <v>6041</v>
       </c>
       <c r="Z8" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA8" s="28" t="n">
-        <v>5034</v>
+        <v>5031</v>
       </c>
       <c r="AB8" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC8" s="28" t="n">
-        <v>6013</v>
+        <v>5019</v>
       </c>
       <c r="AD8" s="28" t="n">
         <v>2500</v>
@@ -2378,20 +2551,20 @@
       </c>
     </row>
     <row r="9" customFormat="1" s="30">
-      <c r="A9" s="23" t="n">
-        <v>2053</v>
+      <c r="A9" s="31" t="n">
+        <v>1058</v>
       </c>
       <c r="B9" s="24" t="n"/>
-      <c r="C9" s="25" t="inlineStr">
-        <is>
-          <t>大白鲸</t>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>小编钟</t>
         </is>
       </c>
       <c r="D9" s="26" t="n">
-        <v>1053</v>
+        <v>1058</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="27" t="n"/>
       <c r="G9" s="27" t="n"/>
@@ -2407,11 +2580,11 @@
         <v>1</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" s="28" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="O9" s="28" t="inlineStr">
@@ -2421,55 +2594,55 @@
       </c>
       <c r="P9" s="28" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q9" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="R9" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S9" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T9" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U9" s="28" t="n">
-        <v>8005</v>
+        <v>8019</v>
       </c>
       <c r="V9" s="28" t="n">
-        <v>5503</v>
+        <v>6027</v>
       </c>
       <c r="W9" s="28" t="n">
-        <v>6553</v>
+        <v>5020</v>
       </c>
       <c r="X9" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>5029</v>
+        <v>5022</v>
       </c>
       <c r="Z9" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA9" s="28" t="n">
-        <v>5034</v>
+        <v>5042</v>
       </c>
       <c r="AB9" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC9" s="28" t="n">
-        <v>6013</v>
+        <v>5013</v>
       </c>
       <c r="AD9" s="28" t="n">
         <v>2500</v>
@@ -2518,20 +2691,20 @@
       </c>
     </row>
     <row r="10" customFormat="1" s="30">
-      <c r="A10" s="23" t="n">
-        <v>3053</v>
+      <c r="A10" s="31" t="n">
+        <v>1059</v>
       </c>
       <c r="B10" s="24" t="n"/>
-      <c r="C10" s="25" t="inlineStr">
-        <is>
-          <t>巨鲸</t>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>小胖墩</t>
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="27" t="n"/>
       <c r="G10" s="27" t="n"/>
@@ -2542,28 +2715,30 @@
         <v>3</v>
       </c>
       <c r="J10" s="24" t="n"/>
-      <c r="K10" s="24" t="n"/>
+      <c r="K10" s="24" t="n">
+        <v>20004</v>
+      </c>
       <c r="L10" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N10" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O10" s="28" t="inlineStr">
         <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="P10" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P10" s="28" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
-      </c>
       <c r="Q10" s="28" t="inlineStr">
         <is>
           <t>1400</t>
@@ -2581,35 +2756,35 @@
       </c>
       <c r="T10" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U10" s="28" t="n">
-        <v>8006</v>
+        <v>8022</v>
       </c>
       <c r="V10" s="28" t="n">
-        <v>5503</v>
+        <v>6019</v>
       </c>
       <c r="W10" s="28" t="n">
-        <v>6553</v>
+        <v>5005</v>
       </c>
       <c r="X10" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y10" s="28" t="n">
-        <v>5029</v>
+        <v>5021</v>
       </c>
       <c r="Z10" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA10" s="28" t="n">
-        <v>5034</v>
+        <v>5003</v>
       </c>
       <c r="AB10" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC10" s="28" t="n">
-        <v>6013</v>
+        <v>5014</v>
       </c>
       <c r="AD10" s="28" t="n">
         <v>2500</v>
@@ -2658,17 +2833,17 @@
       </c>
     </row>
     <row r="11" customFormat="1" s="30">
-      <c r="A11" s="23" t="n">
-        <v>1054</v>
+      <c r="A11" s="31" t="n">
+        <v>1060</v>
       </c>
       <c r="B11" s="24" t="n"/>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>木结花</t>
+          <t>剑灵</t>
         </is>
       </c>
       <c r="D11" s="26" t="n">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="E11" s="26" t="n">
         <v>0</v>
@@ -2687,7 +2862,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N11" s="28" t="inlineStr">
         <is>
@@ -2696,14 +2871,14 @@
       </c>
       <c r="O11" s="28" t="inlineStr">
         <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="P11" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P11" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="Q11" s="28" t="inlineStr">
         <is>
           <t>1200</t>
@@ -2716,7 +2891,7 @@
       </c>
       <c r="S11" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T11" s="28" t="inlineStr">
@@ -2725,31 +2900,31 @@
         </is>
       </c>
       <c r="U11" s="28" t="n">
-        <v>8007</v>
+        <v>8025</v>
       </c>
       <c r="V11" s="28" t="n">
-        <v>5047</v>
+        <v>6044</v>
       </c>
       <c r="W11" s="28" t="n">
-        <v>5022</v>
+        <v>6004</v>
       </c>
       <c r="X11" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>5028</v>
+        <v>5001</v>
       </c>
       <c r="Z11" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>5042</v>
+        <v>5012</v>
       </c>
       <c r="AB11" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC11" s="28" t="n">
-        <v>5026</v>
+        <v>5013</v>
       </c>
       <c r="AD11" s="28" t="n">
         <v>2500</v>
@@ -2798,20 +2973,20 @@
       </c>
     </row>
     <row r="12" customFormat="1" s="30">
-      <c r="A12" s="23" t="n">
-        <v>2054</v>
+      <c r="A12" s="31" t="n">
+        <v>1061</v>
       </c>
       <c r="B12" s="24" t="n"/>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>花精灵</t>
+          <t>模仿玩偶</t>
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="27" t="n"/>
       <c r="G12" s="27" t="n"/>
@@ -2827,11 +3002,11 @@
         <v>1</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="O12" s="28" t="inlineStr">
@@ -2841,55 +3016,55 @@
       </c>
       <c r="P12" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="Q12" s="28" t="inlineStr">
         <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R12" s="28" t="inlineStr">
+        <is>
           <t>1300</t>
         </is>
       </c>
-      <c r="R12" s="28" t="inlineStr">
+      <c r="S12" s="28" t="inlineStr">
         <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="S12" s="28" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
       <c r="T12" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U12" s="28" t="n">
-        <v>8008</v>
+        <v>8028</v>
       </c>
       <c r="V12" s="28" t="n">
-        <v>5047</v>
+        <v>6007</v>
       </c>
       <c r="W12" s="28" t="n">
-        <v>5022</v>
+        <v>6551</v>
       </c>
       <c r="X12" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y12" s="28" t="n">
-        <v>5028</v>
+        <v>5006</v>
       </c>
       <c r="Z12" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA12" s="28" t="n">
-        <v>5042</v>
+        <v>5015</v>
       </c>
       <c r="AB12" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC12" s="28" t="n">
-        <v>5026</v>
+        <v>5010</v>
       </c>
       <c r="AD12" s="28" t="n">
         <v>2500</v>
@@ -2938,20 +3113,20 @@
       </c>
     </row>
     <row r="13" customFormat="1" s="30">
-      <c r="A13" s="23" t="n">
-        <v>3054</v>
+      <c r="A13" s="31" t="n">
+        <v>1062</v>
       </c>
       <c r="B13" s="24" t="n"/>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>蕊花仙</t>
+          <t>铠甲小子</t>
         </is>
       </c>
       <c r="D13" s="26" t="n">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
@@ -2967,23 +3142,23 @@
         <v>1</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N13" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="O13" s="28" t="inlineStr">
         <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="P13" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P13" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="Q13" s="28" t="inlineStr">
         <is>
           <t>1400</t>
@@ -2996,40 +3171,40 @@
       </c>
       <c r="S13" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T13" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U13" s="28" t="n">
-        <v>8009</v>
+        <v>8031</v>
       </c>
       <c r="V13" s="28" t="n">
-        <v>5047</v>
+        <v>6556</v>
       </c>
       <c r="W13" s="28" t="n">
-        <v>5022</v>
+        <v>6030</v>
       </c>
       <c r="X13" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>5028</v>
+        <v>6003</v>
       </c>
       <c r="Z13" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>5042</v>
+        <v>5005</v>
       </c>
       <c r="AB13" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC13" s="28" t="n">
-        <v>5026</v>
+        <v>5019</v>
       </c>
       <c r="AD13" s="28" t="n">
         <v>2500</v>
@@ -3078,17 +3253,17 @@
       </c>
     </row>
     <row r="14" customFormat="1" s="30">
-      <c r="A14" s="23" t="n">
-        <v>1055</v>
+      <c r="A14" s="31" t="n">
+        <v>1063</v>
       </c>
       <c r="B14" s="24" t="n"/>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>小顽蝠</t>
+          <t>白泽一阶</t>
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>0</v>
@@ -3096,7 +3271,7 @@
       <c r="F14" s="27" t="n"/>
       <c r="G14" s="27" t="n"/>
       <c r="H14" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" s="24" t="n">
         <v>3</v>
@@ -3111,65 +3286,65 @@
       </c>
       <c r="N14" s="28" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O14" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="P14" s="28" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="Q14" s="28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="R14" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S14" s="28" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T14" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U14" s="28" t="n">
-        <v>8010</v>
+        <v>8034</v>
       </c>
       <c r="V14" s="28" t="n">
-        <v>5010</v>
+        <v>6007</v>
       </c>
       <c r="W14" s="28" t="n">
-        <v>6554</v>
+        <v>6009</v>
       </c>
       <c r="X14" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y14" s="28" t="n">
-        <v>5037</v>
+        <v>6010</v>
       </c>
       <c r="Z14" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA14" s="28" t="n">
-        <v>5038</v>
+        <v>5021</v>
       </c>
       <c r="AB14" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC14" s="28" t="n">
-        <v>5057</v>
+        <v>5020</v>
       </c>
       <c r="AD14" s="28" t="n">
         <v>2500</v>
@@ -3218,25 +3393,25 @@
       </c>
     </row>
     <row r="15" customFormat="1" s="30">
-      <c r="A15" s="23" t="n">
-        <v>2055</v>
+      <c r="A15" s="31" t="n">
+        <v>1064</v>
       </c>
       <c r="B15" s="24" t="n"/>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>吸血蝠</t>
+          <t>刑天一阶</t>
         </is>
       </c>
       <c r="D15" s="26" t="n">
-        <v>1055</v>
+        <v>1064</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="27" t="n"/>
       <c r="G15" s="27" t="n"/>
       <c r="H15" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" s="24" t="n">
         <v>3</v>
@@ -3247,26 +3422,26 @@
         <v>1</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" s="28" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O15" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="P15" s="28" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="Q15" s="28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="R15" s="28" t="inlineStr">
@@ -3276,7 +3451,7 @@
       </c>
       <c r="S15" s="28" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T15" s="28" t="inlineStr">
@@ -3285,31 +3460,31 @@
         </is>
       </c>
       <c r="U15" s="28" t="n">
-        <v>8011</v>
+        <v>8037</v>
       </c>
       <c r="V15" s="28" t="n">
-        <v>5010</v>
+        <v>6001</v>
       </c>
       <c r="W15" s="28" t="n">
-        <v>6554</v>
+        <v>6014</v>
       </c>
       <c r="X15" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>5037</v>
+        <v>6005</v>
       </c>
       <c r="Z15" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>5038</v>
+        <v>5040</v>
       </c>
       <c r="AB15" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC15" s="28" t="n">
-        <v>5057</v>
+        <v>5003</v>
       </c>
       <c r="AD15" s="28" t="n">
         <v>2500</v>
@@ -3358,25 +3533,25 @@
       </c>
     </row>
     <row r="16" customFormat="1" s="30">
-      <c r="A16" s="23" t="n">
-        <v>3055</v>
+      <c r="A16" s="31" t="n">
+        <v>1065</v>
       </c>
       <c r="B16" s="24" t="n"/>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>霹雳蝠</t>
+          <t>饕餮一阶</t>
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1055</v>
+        <v>1065</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="27" t="n"/>
       <c r="G16" s="27" t="n"/>
       <c r="H16" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" s="24" t="n">
         <v>3</v>
@@ -3387,16 +3562,16 @@
         <v>1</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O16" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="P16" s="28" t="inlineStr">
@@ -3406,50 +3581,50 @@
       </c>
       <c r="Q16" s="28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="R16" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S16" s="28" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T16" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U16" s="28" t="n">
-        <v>8012</v>
+        <v>8040</v>
       </c>
       <c r="V16" s="28" t="n">
-        <v>5010</v>
+        <v>6020</v>
       </c>
       <c r="W16" s="28" t="n">
-        <v>6554</v>
+        <v>6042</v>
       </c>
       <c r="X16" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y16" s="28" t="n">
-        <v>5037</v>
+        <v>6021</v>
       </c>
       <c r="Z16" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA16" s="28" t="n">
-        <v>5038</v>
+        <v>5022</v>
       </c>
       <c r="AB16" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC16" s="28" t="n">
-        <v>5057</v>
+        <v>5047</v>
       </c>
       <c r="AD16" s="28" t="n">
         <v>2500</v>
@@ -3499,19 +3674,19 @@
     </row>
     <row r="17" customFormat="1" s="30">
       <c r="A17" s="23" t="n">
-        <v>1056</v>
+        <v>2052</v>
       </c>
       <c r="B17" s="24" t="n"/>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>慢慢龟</t>
+          <t>烈焰犬</t>
         </is>
       </c>
       <c r="D17" s="26" t="n">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="27" t="n"/>
       <c r="G17" s="27" t="n"/>
@@ -3527,7 +3702,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N17" s="28" t="inlineStr">
         <is>
@@ -3536,14 +3711,14 @@
       </c>
       <c r="O17" s="28" t="inlineStr">
         <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="P17" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P17" s="28" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
       <c r="Q17" s="28" t="inlineStr">
         <is>
           <t>1200</t>
@@ -3551,45 +3726,45 @@
       </c>
       <c r="R17" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S17" s="28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T17" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U17" s="28" t="n">
-        <v>8013</v>
+        <v>8002</v>
       </c>
       <c r="V17" s="28" t="n">
-        <v>5503</v>
+        <v>6556</v>
       </c>
       <c r="W17" s="28" t="n">
-        <v>5025</v>
+        <v>5005</v>
       </c>
       <c r="X17" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>6015</v>
+        <v>6011</v>
       </c>
       <c r="Z17" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA17" s="28" t="n">
-        <v>5009</v>
+        <v>5040</v>
       </c>
       <c r="AB17" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC17" s="28" t="n">
-        <v>6029</v>
+        <v>5046</v>
       </c>
       <c r="AD17" s="28" t="n">
         <v>2500</v>
@@ -3639,16 +3814,16 @@
     </row>
     <row r="18" customFormat="1" s="30">
       <c r="A18" s="23" t="n">
-        <v>2056</v>
+        <v>2053</v>
       </c>
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>勇士龟</t>
+          <t>大白鲸</t>
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>1</v>
@@ -3671,7 +3846,7 @@
       </c>
       <c r="N18" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="O18" s="28" t="inlineStr">
@@ -3691,12 +3866,12 @@
       </c>
       <c r="R18" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S18" s="28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T18" s="28" t="inlineStr">
@@ -3705,31 +3880,31 @@
         </is>
       </c>
       <c r="U18" s="28" t="n">
-        <v>8014</v>
+        <v>8005</v>
       </c>
       <c r="V18" s="28" t="n">
         <v>5503</v>
       </c>
       <c r="W18" s="28" t="n">
-        <v>5025</v>
+        <v>6553</v>
       </c>
       <c r="X18" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y18" s="28" t="n">
-        <v>6015</v>
+        <v>5029</v>
       </c>
       <c r="Z18" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA18" s="28" t="n">
-        <v>5009</v>
+        <v>5034</v>
       </c>
       <c r="AB18" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC18" s="28" t="n">
-        <v>6029</v>
+        <v>6013</v>
       </c>
       <c r="AD18" s="28" t="n">
         <v>2500</v>
@@ -3779,19 +3954,19 @@
     </row>
     <row r="19" customFormat="1" s="30">
       <c r="A19" s="23" t="n">
-        <v>3056</v>
+        <v>2054</v>
       </c>
       <c r="B19" s="24" t="n"/>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>千岁龟</t>
+          <t>花精灵</t>
         </is>
       </c>
       <c r="D19" s="26" t="n">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="27" t="n"/>
       <c r="G19" s="27" t="n"/>
@@ -3807,11 +3982,11 @@
         <v>1</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" s="28" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O19" s="28" t="inlineStr">
@@ -3821,55 +3996,55 @@
       </c>
       <c r="P19" s="28" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q19" s="28" t="inlineStr">
         <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="R19" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S19" s="28" t="inlineStr">
+        <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="R19" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="S19" s="28" t="inlineStr">
-        <is>
-          <t>600</t>
-        </is>
-      </c>
       <c r="T19" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U19" s="28" t="n">
-        <v>8015</v>
+        <v>8008</v>
       </c>
       <c r="V19" s="28" t="n">
-        <v>5503</v>
+        <v>5047</v>
       </c>
       <c r="W19" s="28" t="n">
-        <v>5025</v>
+        <v>5022</v>
       </c>
       <c r="X19" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>6015</v>
+        <v>5028</v>
       </c>
       <c r="Z19" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA19" s="28" t="n">
-        <v>5009</v>
+        <v>5042</v>
       </c>
       <c r="AB19" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC19" s="28" t="n">
-        <v>6029</v>
+        <v>5026</v>
       </c>
       <c r="AD19" s="28" t="n">
         <v>2500</v>
@@ -3918,20 +4093,20 @@
       </c>
     </row>
     <row r="20" customFormat="1" s="30">
-      <c r="A20" s="31" t="n">
-        <v>1057</v>
+      <c r="A20" s="23" t="n">
+        <v>2055</v>
       </c>
       <c r="B20" s="24" t="n"/>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>岩岩石</t>
+          <t>吸血蝠</t>
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
@@ -3947,69 +4122,69 @@
         <v>1</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N20" s="28" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P20" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="Q20" s="28" t="inlineStr">
         <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="R20" s="28" t="inlineStr">
+        <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="R20" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="S20" s="28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T20" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U20" s="28" t="n">
-        <v>8016</v>
+        <v>8011</v>
       </c>
       <c r="V20" s="28" t="n">
-        <v>6022</v>
+        <v>5010</v>
       </c>
       <c r="W20" s="28" t="n">
-        <v>5021</v>
+        <v>6554</v>
       </c>
       <c r="X20" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y20" s="28" t="n">
-        <v>6041</v>
+        <v>5037</v>
       </c>
       <c r="Z20" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA20" s="28" t="n">
-        <v>5031</v>
+        <v>5038</v>
       </c>
       <c r="AB20" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC20" s="28" t="n">
-        <v>5019</v>
+        <v>5057</v>
       </c>
       <c r="AD20" s="28" t="n">
         <v>2500</v>
@@ -4059,16 +4234,16 @@
     </row>
     <row r="21" customFormat="1" s="30">
       <c r="A21" s="23" t="n">
-        <v>2057</v>
+        <v>2056</v>
       </c>
       <c r="B21" s="24" t="n"/>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>多岩小将</t>
+          <t>勇士龟</t>
         </is>
       </c>
       <c r="D21" s="26" t="n">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E21" s="26" t="n">
         <v>1</v>
@@ -4087,36 +4262,36 @@
         <v>1</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N21" s="28" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O21" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P21" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="Q21" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="R21" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S21" s="28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T21" s="28" t="inlineStr">
@@ -4125,31 +4300,31 @@
         </is>
       </c>
       <c r="U21" s="28" t="n">
-        <v>8017</v>
+        <v>8014</v>
       </c>
       <c r="V21" s="28" t="n">
-        <v>6022</v>
+        <v>5503</v>
       </c>
       <c r="W21" s="28" t="n">
-        <v>5021</v>
+        <v>5025</v>
       </c>
       <c r="X21" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>6041</v>
+        <v>6015</v>
       </c>
       <c r="Z21" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>5031</v>
+        <v>5009</v>
       </c>
       <c r="AB21" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC21" s="28" t="n">
-        <v>5019</v>
+        <v>6029</v>
       </c>
       <c r="AD21" s="28" t="n">
         <v>2500</v>
@@ -4199,19 +4374,19 @@
     </row>
     <row r="22" customFormat="1" s="30">
       <c r="A22" s="23" t="n">
-        <v>3057</v>
+        <v>2057</v>
       </c>
       <c r="B22" s="24" t="n"/>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>岩将军</t>
+          <t>多岩小将</t>
         </is>
       </c>
       <c r="D22" s="26" t="n">
         <v>1057</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" s="27" t="n"/>
       <c r="G22" s="27" t="n"/>
@@ -4231,12 +4406,12 @@
       </c>
       <c r="N22" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="O22" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="P22" s="28" t="inlineStr">
@@ -4246,7 +4421,7 @@
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="R22" s="28" t="inlineStr">
@@ -4261,11 +4436,11 @@
       </c>
       <c r="T22" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U22" s="28" t="n">
-        <v>8018</v>
+        <v>8017</v>
       </c>
       <c r="V22" s="28" t="n">
         <v>6022</v>
@@ -4338,20 +4513,20 @@
       </c>
     </row>
     <row r="23" customFormat="1" s="30">
-      <c r="A23" s="31" t="n">
-        <v>1058</v>
+      <c r="A23" s="23" t="n">
+        <v>2058</v>
       </c>
       <c r="B23" s="24" t="n"/>
-      <c r="C23" s="32" t="inlineStr">
-        <is>
-          <t>小编钟</t>
+      <c r="C23" s="33" t="inlineStr">
+        <is>
+          <t>青铜钟偶</t>
         </is>
       </c>
       <c r="D23" s="26" t="n">
         <v>1058</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
@@ -4371,7 +4546,7 @@
       </c>
       <c r="N23" s="28" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O23" s="28" t="inlineStr">
@@ -4391,21 +4566,21 @@
       </c>
       <c r="R23" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S23" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T23" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U23" s="28" t="n">
-        <v>8019</v>
+        <v>8020</v>
       </c>
       <c r="V23" s="28" t="n">
         <v>6027</v>
@@ -4479,16 +4654,16 @@
     </row>
     <row r="24" customFormat="1" s="30">
       <c r="A24" s="23" t="n">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>青铜钟偶</t>
+          <t>贪吃鬼</t>
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E24" s="26" t="n">
         <v>1</v>
@@ -4507,69 +4682,69 @@
         <v>1</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N24" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O24" s="28" t="inlineStr">
         <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="P24" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P24" s="28" t="inlineStr">
+      <c r="Q24" s="28" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="R24" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S24" s="28" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="Q24" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="R24" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="S24" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
       <c r="T24" s="28" t="inlineStr">
         <is>
           <t>1.2</t>
         </is>
       </c>
       <c r="U24" s="28" t="n">
-        <v>8020</v>
+        <v>8023</v>
       </c>
       <c r="V24" s="28" t="n">
-        <v>6027</v>
+        <v>6019</v>
       </c>
       <c r="W24" s="28" t="n">
-        <v>5020</v>
+        <v>5005</v>
       </c>
       <c r="X24" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y24" s="28" t="n">
-        <v>5022</v>
+        <v>5021</v>
       </c>
       <c r="Z24" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA24" s="28" t="n">
-        <v>5042</v>
+        <v>5003</v>
       </c>
       <c r="AB24" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC24" s="28" t="n">
-        <v>5013</v>
+        <v>5014</v>
       </c>
       <c r="AD24" s="28" t="n">
         <v>2500</v>
@@ -4619,19 +4794,19 @@
     </row>
     <row r="25" customFormat="1" s="30">
       <c r="A25" s="23" t="n">
-        <v>3058</v>
+        <v>2060</v>
       </c>
       <c r="B25" s="24" t="n"/>
-      <c r="C25" s="33" t="inlineStr">
-        <is>
-          <t>远古编钟</t>
+      <c r="C25" s="25" t="inlineStr">
+        <is>
+          <t>鬼剑</t>
         </is>
       </c>
       <c r="D25" s="26" t="n">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="27" t="n"/>
       <c r="G25" s="27" t="n"/>
@@ -4647,23 +4822,23 @@
         <v>1</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N25" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O25" s="28" t="inlineStr">
         <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="P25" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P25" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="Q25" s="28" t="inlineStr">
         <is>
           <t>1200</t>
@@ -4671,39 +4846,39 @@
       </c>
       <c r="R25" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S25" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T25" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U25" s="28" t="n">
-        <v>8021</v>
+        <v>8026</v>
       </c>
       <c r="V25" s="28" t="n">
-        <v>6027</v>
+        <v>6044</v>
       </c>
       <c r="W25" s="28" t="n">
-        <v>5020</v>
+        <v>6004</v>
       </c>
       <c r="X25" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y25" s="28" t="n">
-        <v>5022</v>
+        <v>5001</v>
       </c>
       <c r="Z25" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA25" s="28" t="n">
-        <v>5042</v>
+        <v>5012</v>
       </c>
       <c r="AB25" s="28" t="n">
         <v>2500</v>
@@ -4758,20 +4933,20 @@
       </c>
     </row>
     <row r="26" customFormat="1" s="30">
-      <c r="A26" s="31" t="n">
-        <v>1059</v>
+      <c r="A26" s="23" t="n">
+        <v>2061</v>
       </c>
       <c r="B26" s="24" t="n"/>
-      <c r="C26" s="32" t="inlineStr">
-        <is>
-          <t>小胖墩</t>
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>双影玩偶</t>
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="27" t="n"/>
       <c r="G26" s="27" t="n"/>
@@ -4782,76 +4957,74 @@
         <v>3</v>
       </c>
       <c r="J26" s="24" t="n"/>
-      <c r="K26" s="24" t="n">
-        <v>20004</v>
-      </c>
+      <c r="K26" s="24" t="n"/>
       <c r="L26" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N26" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O26" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="Q26" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="R26" s="28" t="inlineStr">
         <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="S26" s="28" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="S26" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="T26" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U26" s="28" t="n">
-        <v>8022</v>
+        <v>8029</v>
       </c>
       <c r="V26" s="28" t="n">
-        <v>6019</v>
+        <v>6007</v>
       </c>
       <c r="W26" s="28" t="n">
-        <v>5005</v>
+        <v>6551</v>
       </c>
       <c r="X26" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y26" s="28" t="n">
-        <v>5021</v>
+        <v>5006</v>
       </c>
       <c r="Z26" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA26" s="28" t="n">
-        <v>5003</v>
+        <v>5015</v>
       </c>
       <c r="AB26" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC26" s="28" t="n">
-        <v>5014</v>
+        <v>5010</v>
       </c>
       <c r="AD26" s="28" t="n">
         <v>2500</v>
@@ -4901,16 +5074,16 @@
     </row>
     <row r="27" customFormat="1" s="30">
       <c r="A27" s="23" t="n">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="B27" s="24" t="n"/>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>贪吃鬼</t>
+      <c r="C27" s="25" t="inlineStr">
+        <is>
+          <t>红莲卫兵</t>
         </is>
       </c>
       <c r="D27" s="26" t="n">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>1</v>
@@ -4933,12 +5106,12 @@
       </c>
       <c r="N27" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O27" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="P27" s="28" t="inlineStr">
@@ -4958,7 +5131,7 @@
       </c>
       <c r="S27" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T27" s="28" t="inlineStr">
@@ -4967,31 +5140,31 @@
         </is>
       </c>
       <c r="U27" s="28" t="n">
-        <v>8023</v>
+        <v>8032</v>
       </c>
       <c r="V27" s="28" t="n">
-        <v>6019</v>
+        <v>6556</v>
       </c>
       <c r="W27" s="28" t="n">
+        <v>6030</v>
+      </c>
+      <c r="X27" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Y27" s="28" t="n">
+        <v>6003</v>
+      </c>
+      <c r="Z27" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AA27" s="28" t="n">
         <v>5005</v>
       </c>
-      <c r="X27" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Y27" s="28" t="n">
-        <v>5021</v>
-      </c>
-      <c r="Z27" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AA27" s="28" t="n">
-        <v>5003</v>
-      </c>
       <c r="AB27" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC27" s="28" t="n">
-        <v>5014</v>
+        <v>5019</v>
       </c>
       <c r="AD27" s="28" t="n">
         <v>2500</v>
@@ -5041,24 +5214,24 @@
     </row>
     <row r="28" customFormat="1" s="30">
       <c r="A28" s="23" t="n">
-        <v>3059</v>
+        <v>2063</v>
       </c>
       <c r="B28" s="24" t="n"/>
-      <c r="C28" s="32" t="inlineStr">
-        <is>
-          <t>坚韧勇士</t>
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>白泽二阶</t>
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="27" t="n"/>
       <c r="G28" s="27" t="n"/>
       <c r="H28" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>3</v>
@@ -5069,11 +5242,11 @@
         <v>1</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N28" s="28" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O28" s="28" t="inlineStr">
@@ -5083,22 +5256,22 @@
       </c>
       <c r="P28" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="Q28" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="R28" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S28" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T28" s="28" t="inlineStr">
@@ -5107,31 +5280,31 @@
         </is>
       </c>
       <c r="U28" s="28" t="n">
-        <v>8024</v>
+        <v>8035</v>
       </c>
       <c r="V28" s="28" t="n">
-        <v>6019</v>
+        <v>6007</v>
       </c>
       <c r="W28" s="28" t="n">
-        <v>5005</v>
+        <v>6009</v>
       </c>
       <c r="X28" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y28" s="28" t="n">
+        <v>6010</v>
+      </c>
+      <c r="Z28" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AA28" s="28" t="n">
         <v>5021</v>
       </c>
-      <c r="Z28" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AA28" s="28" t="n">
-        <v>5003</v>
-      </c>
       <c r="AB28" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC28" s="28" t="n">
-        <v>5014</v>
+        <v>5020</v>
       </c>
       <c r="AD28" s="28" t="n">
         <v>2500</v>
@@ -5180,25 +5353,25 @@
       </c>
     </row>
     <row r="29" customFormat="1" s="30">
-      <c r="A29" s="31" t="n">
-        <v>1060</v>
+      <c r="A29" s="23" t="n">
+        <v>2064</v>
       </c>
       <c r="B29" s="24" t="n"/>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>剑灵</t>
+          <t>刑天二阶</t>
         </is>
       </c>
       <c r="D29" s="26" t="n">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="27" t="n"/>
       <c r="G29" s="27" t="n"/>
       <c r="H29" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>3</v>
@@ -5213,7 +5386,7 @@
       </c>
       <c r="N29" s="28" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O29" s="28" t="inlineStr">
@@ -5223,55 +5396,55 @@
       </c>
       <c r="P29" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="Q29" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="R29" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S29" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T29" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U29" s="28" t="n">
-        <v>8025</v>
+        <v>8038</v>
       </c>
       <c r="V29" s="28" t="n">
-        <v>6044</v>
+        <v>6001</v>
       </c>
       <c r="W29" s="28" t="n">
-        <v>6004</v>
+        <v>6014</v>
       </c>
       <c r="X29" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y29" s="28" t="n">
-        <v>5001</v>
+        <v>6005</v>
       </c>
       <c r="Z29" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA29" s="28" t="n">
-        <v>5012</v>
+        <v>5040</v>
       </c>
       <c r="AB29" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC29" s="28" t="n">
-        <v>5013</v>
+        <v>5003</v>
       </c>
       <c r="AD29" s="28" t="n">
         <v>2500</v>
@@ -5321,16 +5494,16 @@
     </row>
     <row r="30" customFormat="1" s="30">
       <c r="A30" s="23" t="n">
-        <v>2060</v>
+        <v>2065</v>
       </c>
       <c r="B30" s="24" t="n"/>
       <c r="C30" s="25" t="inlineStr">
         <is>
-          <t>鬼剑</t>
+          <t>饕餮二阶</t>
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>1060</v>
+        <v>1065</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>1</v>
@@ -5338,7 +5511,7 @@
       <c r="F30" s="27" t="n"/>
       <c r="G30" s="27" t="n"/>
       <c r="H30" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>3</v>
@@ -5349,31 +5522,31 @@
         <v>1</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N30" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O30" s="28" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="P30" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="Q30" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="R30" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S30" s="28" t="inlineStr">
@@ -5383,35 +5556,35 @@
       </c>
       <c r="T30" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U30" s="28" t="n">
-        <v>8026</v>
+        <v>8041</v>
       </c>
       <c r="V30" s="28" t="n">
-        <v>6044</v>
+        <v>6020</v>
       </c>
       <c r="W30" s="28" t="n">
-        <v>6004</v>
+        <v>6042</v>
       </c>
       <c r="X30" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y30" s="28" t="n">
-        <v>5001</v>
+        <v>6021</v>
       </c>
       <c r="Z30" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA30" s="28" t="n">
-        <v>5012</v>
+        <v>5022</v>
       </c>
       <c r="AB30" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC30" s="28" t="n">
-        <v>5013</v>
+        <v>5047</v>
       </c>
       <c r="AD30" s="28" t="n">
         <v>2500</v>
@@ -5461,16 +5634,16 @@
     </row>
     <row r="31" customFormat="1" s="30">
       <c r="A31" s="23" t="n">
-        <v>3060</v>
+        <v>3052</v>
       </c>
       <c r="B31" s="24" t="n"/>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>天穹剑</t>
+          <t>炽焰獒</t>
         </is>
       </c>
       <c r="D31" s="26" t="n">
-        <v>1060</v>
+        <v>1052</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>2</v>
@@ -5493,12 +5666,12 @@
       </c>
       <c r="N31" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O31" s="28" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="P31" s="28" t="inlineStr">
@@ -5518,7 +5691,7 @@
       </c>
       <c r="S31" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T31" s="28" t="inlineStr">
@@ -5527,31 +5700,31 @@
         </is>
       </c>
       <c r="U31" s="28" t="n">
-        <v>8027</v>
+        <v>8003</v>
       </c>
       <c r="V31" s="28" t="n">
-        <v>6044</v>
+        <v>6556</v>
       </c>
       <c r="W31" s="28" t="n">
-        <v>6004</v>
+        <v>5005</v>
       </c>
       <c r="X31" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y31" s="28" t="n">
-        <v>5001</v>
+        <v>6011</v>
       </c>
       <c r="Z31" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA31" s="28" t="n">
-        <v>5012</v>
+        <v>5040</v>
       </c>
       <c r="AB31" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC31" s="28" t="n">
-        <v>5013</v>
+        <v>5046</v>
       </c>
       <c r="AD31" s="28" t="n">
         <v>2500</v>
@@ -5600,20 +5773,20 @@
       </c>
     </row>
     <row r="32" customFormat="1" s="30">
-      <c r="A32" s="31" t="n">
-        <v>1061</v>
+      <c r="A32" s="23" t="n">
+        <v>3053</v>
       </c>
       <c r="B32" s="24" t="n"/>
       <c r="C32" s="25" t="inlineStr">
         <is>
-          <t>模仿玩偶</t>
+          <t>巨鲸</t>
         </is>
       </c>
       <c r="D32" s="26" t="n">
-        <v>1061</v>
+        <v>1053</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F32" s="27" t="n"/>
       <c r="G32" s="27" t="n"/>
@@ -5633,7 +5806,7 @@
       </c>
       <c r="N32" s="28" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O32" s="28" t="inlineStr">
@@ -5648,50 +5821,50 @@
       </c>
       <c r="Q32" s="28" t="inlineStr">
         <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="R32" s="28" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="R32" s="28" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
       <c r="S32" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T32" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U32" s="28" t="n">
-        <v>8028</v>
+        <v>8006</v>
       </c>
       <c r="V32" s="28" t="n">
-        <v>6007</v>
+        <v>5503</v>
       </c>
       <c r="W32" s="28" t="n">
-        <v>6551</v>
+        <v>6553</v>
       </c>
       <c r="X32" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y32" s="28" t="n">
-        <v>5006</v>
+        <v>5029</v>
       </c>
       <c r="Z32" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA32" s="28" t="n">
-        <v>5015</v>
+        <v>5034</v>
       </c>
       <c r="AB32" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC32" s="28" t="n">
-        <v>5010</v>
+        <v>6013</v>
       </c>
       <c r="AD32" s="28" t="n">
         <v>2500</v>
@@ -5741,19 +5914,19 @@
     </row>
     <row r="33" customFormat="1" s="30">
       <c r="A33" s="23" t="n">
-        <v>2061</v>
+        <v>3054</v>
       </c>
       <c r="B33" s="24" t="n"/>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>双影玩偶</t>
+          <t>蕊花仙</t>
         </is>
       </c>
       <c r="D33" s="26" t="n">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
@@ -5769,11 +5942,11 @@
         <v>1</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O33" s="28" t="inlineStr">
@@ -5783,55 +5956,55 @@
       </c>
       <c r="P33" s="28" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q33" s="28" t="inlineStr">
         <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="R33" s="28" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="R33" s="28" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
       <c r="S33" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T33" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U33" s="28" t="n">
-        <v>8029</v>
+        <v>8009</v>
       </c>
       <c r="V33" s="28" t="n">
-        <v>6007</v>
+        <v>5047</v>
       </c>
       <c r="W33" s="28" t="n">
-        <v>6551</v>
+        <v>5022</v>
       </c>
       <c r="X33" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y33" s="28" t="n">
-        <v>5006</v>
+        <v>5028</v>
       </c>
       <c r="Z33" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA33" s="28" t="n">
-        <v>5015</v>
+        <v>5042</v>
       </c>
       <c r="AB33" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC33" s="28" t="n">
-        <v>5010</v>
+        <v>5026</v>
       </c>
       <c r="AD33" s="28" t="n">
         <v>2500</v>
@@ -5881,16 +6054,16 @@
     </row>
     <row r="34" customFormat="1" s="30">
       <c r="A34" s="23" t="n">
-        <v>3061</v>
+        <v>3055</v>
       </c>
       <c r="B34" s="24" t="n"/>
       <c r="C34" s="25" t="inlineStr">
         <is>
-          <t>镜面玩偶</t>
+          <t>霹雳蝠</t>
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="E34" s="26" t="n">
         <v>2</v>
@@ -5913,7 +6086,7 @@
       </c>
       <c r="N34" s="28" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O34" s="28" t="inlineStr">
@@ -5923,22 +6096,22 @@
       </c>
       <c r="P34" s="28" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="Q34" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="R34" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S34" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T34" s="28" t="inlineStr">
@@ -5947,31 +6120,31 @@
         </is>
       </c>
       <c r="U34" s="28" t="n">
-        <v>8030</v>
+        <v>8012</v>
       </c>
       <c r="V34" s="28" t="n">
-        <v>6007</v>
+        <v>5010</v>
       </c>
       <c r="W34" s="28" t="n">
-        <v>6551</v>
+        <v>6554</v>
       </c>
       <c r="X34" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y34" s="28" t="n">
-        <v>5006</v>
+        <v>5037</v>
       </c>
       <c r="Z34" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA34" s="28" t="n">
-        <v>5015</v>
+        <v>5038</v>
       </c>
       <c r="AB34" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC34" s="28" t="n">
-        <v>5010</v>
+        <v>5057</v>
       </c>
       <c r="AD34" s="28" t="n">
         <v>2500</v>
@@ -6020,20 +6193,20 @@
       </c>
     </row>
     <row r="35" customFormat="1" s="30">
-      <c r="A35" s="31" t="n">
-        <v>1062</v>
+      <c r="A35" s="23" t="n">
+        <v>3056</v>
       </c>
       <c r="B35" s="24" t="n"/>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>铠甲小子</t>
+          <t>千岁龟</t>
         </is>
       </c>
       <c r="D35" s="26" t="n">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" s="27" t="n"/>
       <c r="G35" s="27" t="n"/>
@@ -6049,21 +6222,21 @@
         <v>1</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" s="28" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="O35" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P35" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="Q35" s="28" t="inlineStr">
@@ -6073,45 +6246,45 @@
       </c>
       <c r="R35" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S35" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T35" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U35" s="28" t="n">
-        <v>8031</v>
+        <v>8015</v>
       </c>
       <c r="V35" s="28" t="n">
-        <v>6556</v>
+        <v>5503</v>
       </c>
       <c r="W35" s="28" t="n">
-        <v>6030</v>
+        <v>5025</v>
       </c>
       <c r="X35" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y35" s="28" t="n">
-        <v>6003</v>
+        <v>6015</v>
       </c>
       <c r="Z35" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA35" s="28" t="n">
-        <v>5005</v>
+        <v>5009</v>
       </c>
       <c r="AB35" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC35" s="28" t="n">
-        <v>5019</v>
+        <v>6029</v>
       </c>
       <c r="AD35" s="28" t="n">
         <v>2500</v>
@@ -6161,19 +6334,19 @@
     </row>
     <row r="36" customFormat="1" s="30">
       <c r="A36" s="23" t="n">
-        <v>2062</v>
+        <v>3057</v>
       </c>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="25" t="inlineStr">
         <is>
-          <t>红莲卫兵</t>
+          <t>岩将军</t>
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="27" t="n"/>
       <c r="G36" s="27" t="n"/>
@@ -6198,7 +6371,7 @@
       </c>
       <c r="O36" s="28" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="P36" s="28" t="inlineStr">
@@ -6208,44 +6381,44 @@
       </c>
       <c r="Q36" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R36" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S36" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T36" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U36" s="28" t="n">
-        <v>8032</v>
+        <v>8018</v>
       </c>
       <c r="V36" s="28" t="n">
-        <v>6556</v>
+        <v>6022</v>
       </c>
       <c r="W36" s="28" t="n">
-        <v>6030</v>
+        <v>5021</v>
       </c>
       <c r="X36" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y36" s="28" t="n">
-        <v>6003</v>
+        <v>6041</v>
       </c>
       <c r="Z36" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA36" s="28" t="n">
-        <v>5005</v>
+        <v>5031</v>
       </c>
       <c r="AB36" s="28" t="n">
         <v>2500</v>
@@ -6301,16 +6474,16 @@
     </row>
     <row r="37" customFormat="1" s="30">
       <c r="A37" s="23" t="n">
-        <v>3062</v>
+        <v>3058</v>
       </c>
       <c r="B37" s="24" t="n"/>
-      <c r="C37" s="25" t="inlineStr">
-        <is>
-          <t>苍炎骑士</t>
+      <c r="C37" s="33" t="inlineStr">
+        <is>
+          <t>远古编钟</t>
         </is>
       </c>
       <c r="D37" s="26" t="n">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="E37" s="26" t="n">
         <v>2</v>
@@ -6329,7 +6502,7 @@
         <v>1</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N37" s="28" t="inlineStr">
         <is>
@@ -6338,7 +6511,7 @@
       </c>
       <c r="O37" s="28" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P37" s="28" t="inlineStr">
@@ -6348,17 +6521,17 @@
       </c>
       <c r="Q37" s="28" t="inlineStr">
         <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R37" s="28" t="inlineStr">
+        <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="R37" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
       <c r="S37" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="T37" s="28" t="inlineStr">
@@ -6367,31 +6540,31 @@
         </is>
       </c>
       <c r="U37" s="28" t="n">
-        <v>8033</v>
+        <v>8021</v>
       </c>
       <c r="V37" s="28" t="n">
-        <v>6556</v>
+        <v>6027</v>
       </c>
       <c r="W37" s="28" t="n">
-        <v>6030</v>
+        <v>5020</v>
       </c>
       <c r="X37" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y37" s="28" t="n">
-        <v>6003</v>
+        <v>5022</v>
       </c>
       <c r="Z37" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA37" s="28" t="n">
-        <v>5005</v>
+        <v>5042</v>
       </c>
       <c r="AB37" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC37" s="28" t="n">
-        <v>5019</v>
+        <v>5013</v>
       </c>
       <c r="AD37" s="28" t="n">
         <v>2500</v>
@@ -6440,25 +6613,25 @@
       </c>
     </row>
     <row r="38" customFormat="1" s="30">
-      <c r="A38" s="31" t="n">
-        <v>1063</v>
+      <c r="A38" s="23" t="n">
+        <v>3059</v>
       </c>
       <c r="B38" s="24" t="n"/>
-      <c r="C38" s="25" t="inlineStr">
-        <is>
-          <t>白泽一阶</t>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>坚韧勇士</t>
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
       <c r="H38" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I38" s="24" t="n">
         <v>3</v>
@@ -6469,69 +6642,69 @@
         <v>1</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N38" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="O38" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="P38" s="28" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q38" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R38" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S38" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T38" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U38" s="28" t="n">
-        <v>8034</v>
+        <v>8024</v>
       </c>
       <c r="V38" s="28" t="n">
-        <v>6007</v>
+        <v>6019</v>
       </c>
       <c r="W38" s="28" t="n">
-        <v>6009</v>
+        <v>5005</v>
       </c>
       <c r="X38" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y38" s="28" t="n">
-        <v>6010</v>
+        <v>5021</v>
       </c>
       <c r="Z38" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA38" s="28" t="n">
-        <v>5021</v>
+        <v>5003</v>
       </c>
       <c r="AB38" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC38" s="28" t="n">
-        <v>5020</v>
+        <v>5014</v>
       </c>
       <c r="AD38" s="28" t="n">
         <v>2500</v>
@@ -6581,24 +6754,24 @@
     </row>
     <row r="39" customFormat="1" s="30">
       <c r="A39" s="23" t="n">
-        <v>2063</v>
+        <v>3060</v>
       </c>
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>白泽二阶</t>
+          <t>天穹剑</t>
         </is>
       </c>
       <c r="D39" s="26" t="n">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="27" t="n"/>
       <c r="G39" s="27" t="n"/>
       <c r="H39" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>3</v>
@@ -6609,7 +6782,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N39" s="28" t="inlineStr">
         <is>
@@ -6618,60 +6791,60 @@
       </c>
       <c r="O39" s="28" t="inlineStr">
         <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="P39" s="28" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="Q39" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R39" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S39" s="28" t="inlineStr">
+        <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="P39" s="28" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="Q39" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="R39" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="S39" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
       <c r="T39" s="28" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
       <c r="U39" s="28" t="n">
-        <v>8035</v>
+        <v>8027</v>
       </c>
       <c r="V39" s="28" t="n">
-        <v>6007</v>
+        <v>6044</v>
       </c>
       <c r="W39" s="28" t="n">
-        <v>6009</v>
+        <v>6004</v>
       </c>
       <c r="X39" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y39" s="28" t="n">
-        <v>6010</v>
+        <v>5001</v>
       </c>
       <c r="Z39" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA39" s="28" t="n">
-        <v>5021</v>
+        <v>5012</v>
       </c>
       <c r="AB39" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC39" s="28" t="n">
-        <v>5020</v>
+        <v>5013</v>
       </c>
       <c r="AD39" s="28" t="n">
         <v>2500</v>
@@ -6721,16 +6894,16 @@
     </row>
     <row r="40" customFormat="1" s="30">
       <c r="A40" s="23" t="n">
-        <v>3063</v>
+        <v>3061</v>
       </c>
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="25" t="inlineStr">
         <is>
-          <t>白泽三阶</t>
+          <t>镜面玩偶</t>
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="E40" s="26" t="n">
         <v>2</v>
@@ -6738,7 +6911,7 @@
       <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
       <c r="H40" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I40" s="24" t="n">
         <v>3</v>
@@ -6753,65 +6926,65 @@
       </c>
       <c r="N40" s="28" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="O40" s="28" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P40" s="28" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="Q40" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="R40" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S40" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T40" s="28" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U40" s="28" t="n">
-        <v>8036</v>
+        <v>8030</v>
       </c>
       <c r="V40" s="28" t="n">
         <v>6007</v>
       </c>
       <c r="W40" s="28" t="n">
-        <v>6009</v>
+        <v>6551</v>
       </c>
       <c r="X40" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y40" s="28" t="n">
-        <v>6010</v>
+        <v>5006</v>
       </c>
       <c r="Z40" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA40" s="28" t="n">
-        <v>5021</v>
+        <v>5015</v>
       </c>
       <c r="AB40" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC40" s="28" t="n">
-        <v>5020</v>
+        <v>5010</v>
       </c>
       <c r="AD40" s="28" t="n">
         <v>2500</v>
@@ -6860,25 +7033,25 @@
       </c>
     </row>
     <row r="41" customFormat="1" s="30">
-      <c r="A41" s="31" t="n">
-        <v>1064</v>
+      <c r="A41" s="23" t="n">
+        <v>3062</v>
       </c>
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>刑天一阶</t>
+          <t>苍炎骑士</t>
         </is>
       </c>
       <c r="D41" s="26" t="n">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
       <c r="H41" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" s="24" t="n">
         <v>3</v>
@@ -6893,65 +7066,65 @@
       </c>
       <c r="N41" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O41" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1700</t>
         </is>
       </c>
       <c r="P41" s="28" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q41" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R41" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S41" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T41" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U41" s="28" t="n">
-        <v>8037</v>
+        <v>8033</v>
       </c>
       <c r="V41" s="28" t="n">
-        <v>6001</v>
+        <v>6556</v>
       </c>
       <c r="W41" s="28" t="n">
-        <v>6014</v>
+        <v>6030</v>
       </c>
       <c r="X41" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y41" s="28" t="n">
-        <v>6005</v>
+        <v>6003</v>
       </c>
       <c r="Z41" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA41" s="28" t="n">
-        <v>5040</v>
+        <v>5005</v>
       </c>
       <c r="AB41" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC41" s="28" t="n">
-        <v>5003</v>
+        <v>5019</v>
       </c>
       <c r="AD41" s="28" t="n">
         <v>2500</v>
@@ -7001,19 +7174,19 @@
     </row>
     <row r="42" customFormat="1" s="30">
       <c r="A42" s="23" t="n">
-        <v>2064</v>
+        <v>3063</v>
       </c>
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="25" t="inlineStr">
         <is>
-          <t>刑天二阶</t>
+          <t>白泽三阶</t>
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="27" t="n"/>
       <c r="G42" s="27" t="n"/>
@@ -7029,69 +7202,69 @@
         <v>1</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N42" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="O42" s="28" t="inlineStr">
         <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="P42" s="28" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="Q42" s="28" t="inlineStr">
+        <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="P42" s="28" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="Q42" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
       <c r="R42" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="S42" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="T42" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="U42" s="28" t="n">
-        <v>8038</v>
+        <v>8036</v>
       </c>
       <c r="V42" s="28" t="n">
-        <v>6001</v>
+        <v>6007</v>
       </c>
       <c r="W42" s="28" t="n">
-        <v>6014</v>
+        <v>6009</v>
       </c>
       <c r="X42" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y42" s="28" t="n">
-        <v>6005</v>
+        <v>6010</v>
       </c>
       <c r="Z42" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA42" s="28" t="n">
-        <v>5040</v>
+        <v>5021</v>
       </c>
       <c r="AB42" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC42" s="28" t="n">
-        <v>5003</v>
+        <v>5020</v>
       </c>
       <c r="AD42" s="28" t="n">
         <v>2500</v>
@@ -7280,20 +7453,20 @@
       </c>
     </row>
     <row r="44" customFormat="1" s="30">
-      <c r="A44" s="31" t="n">
-        <v>1065</v>
+      <c r="A44" s="23" t="n">
+        <v>3065</v>
       </c>
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="25" t="inlineStr">
         <is>
-          <t>饕餮一阶</t>
+          <t>饕餮三阶</t>
         </is>
       </c>
       <c r="D44" s="26" t="n">
         <v>1065</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" s="27" t="n"/>
       <c r="G44" s="27" t="n"/>
@@ -7313,41 +7486,41 @@
       </c>
       <c r="N44" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="O44" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="P44" s="28" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="Q44" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R44" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="S44" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="T44" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="U44" s="28" t="n">
-        <v>8040</v>
+        <v>8042</v>
       </c>
       <c r="V44" s="28" t="n">
         <v>6020</v>
@@ -7421,287 +7594,219 @@
     </row>
     <row r="45" customFormat="1" s="30">
       <c r="A45" s="23" t="n">
-        <v>2065</v>
+        <v>3066</v>
       </c>
       <c r="B45" s="24" t="n"/>
       <c r="C45" s="25" t="inlineStr">
         <is>
-          <t>饕餮二阶</t>
+          <t>九尾天狐</t>
         </is>
       </c>
       <c r="D45" s="26" t="n">
-        <v>1065</v>
-      </c>
-      <c r="E45" s="26" t="n">
-        <v>1</v>
-      </c>
+        <v>1070</v>
+      </c>
+      <c r="E45" s="26" t="n"/>
       <c r="F45" s="27" t="n"/>
       <c r="G45" s="27" t="n"/>
-      <c r="H45" s="24" t="n">
-        <v>2</v>
-      </c>
+      <c r="H45" s="24" t="n"/>
       <c r="I45" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J45" s="24" t="n"/>
-      <c r="K45" s="24" t="n"/>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="n">
+        <v>28999</v>
+      </c>
       <c r="L45" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N45" s="28" t="inlineStr">
-        <is>
-          <t>5200</t>
-        </is>
-      </c>
-      <c r="O45" s="28" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="P45" s="28" t="inlineStr">
-        <is>
-          <t>2800</t>
-        </is>
-      </c>
-      <c r="Q45" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="R45" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="S45" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="T45" s="28" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="U45" s="28" t="n">
-        <v>8041</v>
-      </c>
-      <c r="V45" s="28" t="n">
-        <v>6020</v>
-      </c>
-      <c r="W45" s="28" t="n">
-        <v>6042</v>
-      </c>
-      <c r="X45" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Y45" s="28" t="n">
-        <v>6021</v>
-      </c>
-      <c r="Z45" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AA45" s="28" t="n">
-        <v>5022</v>
-      </c>
-      <c r="AB45" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AC45" s="28" t="n">
-        <v>5047</v>
-      </c>
-      <c r="AD45" s="28" t="n">
-        <v>2500</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="M45" s="27" t="n"/>
+      <c r="N45" s="28" t="n">
+        <v>6000</v>
+      </c>
+      <c r="O45" s="28" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P45" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Q45" s="28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R45" s="28" t="n">
+        <v>1500</v>
+      </c>
+      <c r="S45" s="28" t="n"/>
+      <c r="T45" s="28" t="n"/>
+      <c r="U45" s="28" t="n"/>
+      <c r="V45" s="28" t="n"/>
+      <c r="W45" s="28" t="n"/>
+      <c r="X45" s="28" t="n"/>
+      <c r="Y45" s="28" t="n"/>
+      <c r="Z45" s="28" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="28" t="n"/>
+      <c r="AD45" s="28" t="n"/>
       <c r="AE45" s="29" t="n"/>
       <c r="AF45" s="29" t="n"/>
       <c r="AG45" s="29" t="n"/>
       <c r="AH45" s="29" t="n"/>
-      <c r="AI45" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ45" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK45" s="28" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="AL45" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM45" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN45" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO45" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP45" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AQ45" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AR45" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" s="28" t="n">
-        <v>10</v>
-      </c>
+      <c r="AI45" s="28" t="n"/>
+      <c r="AJ45" s="28" t="n"/>
+      <c r="AK45" s="28" t="n"/>
+      <c r="AL45" s="28" t="n"/>
+      <c r="AM45" s="28" t="n"/>
+      <c r="AN45" s="28" t="n"/>
+      <c r="AO45" s="28" t="n"/>
+      <c r="AP45" s="28" t="n"/>
+      <c r="AQ45" s="28" t="n"/>
+      <c r="AR45" s="28" t="n"/>
+      <c r="AS45" s="28" t="n"/>
+      <c r="AT45" s="28" t="n"/>
     </row>
     <row r="46" customFormat="1" s="30">
-      <c r="A46" s="23" t="n">
-        <v>3065</v>
-      </c>
-      <c r="B46" s="24" t="n"/>
-      <c r="C46" s="25" t="inlineStr">
-        <is>
-          <t>饕餮三阶</t>
-        </is>
-      </c>
-      <c r="D46" s="26" t="n">
-        <v>1065</v>
-      </c>
-      <c r="E46" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F46" s="27" t="n"/>
-      <c r="G46" s="27" t="n"/>
-      <c r="H46" s="24" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="J46" s="24" t="n"/>
-      <c r="K46" s="24" t="n"/>
-      <c r="L46" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="N46" s="28" t="inlineStr">
-        <is>
-          <t>5400</t>
-        </is>
-      </c>
-      <c r="O46" s="28" t="inlineStr">
-        <is>
-          <t>1650</t>
-        </is>
-      </c>
-      <c r="P46" s="28" t="inlineStr">
-        <is>
-          <t>2900</t>
-        </is>
-      </c>
-      <c r="Q46" s="28" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="R46" s="28" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="S46" s="28" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
-      <c r="T46" s="28" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
-      </c>
-      <c r="U46" s="28" t="n">
-        <v>8042</v>
-      </c>
-      <c r="V46" s="28" t="n">
-        <v>6020</v>
-      </c>
-      <c r="W46" s="28" t="n">
-        <v>6042</v>
-      </c>
-      <c r="X46" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Y46" s="28" t="n">
-        <v>6021</v>
-      </c>
-      <c r="Z46" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AA46" s="28" t="n">
-        <v>5022</v>
-      </c>
-      <c r="AB46" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AC46" s="28" t="n">
-        <v>5047</v>
-      </c>
-      <c r="AD46" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AE46" s="29" t="n"/>
-      <c r="AF46" s="29" t="n"/>
-      <c r="AG46" s="29" t="n"/>
-      <c r="AH46" s="29" t="n"/>
-      <c r="AI46" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ46" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK46" s="28" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="AL46" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM46" s="28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN46" s="28" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO46" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP46" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AQ46" s="28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AR46" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" s="28" t="n">
-        <v>10</v>
-      </c>
+      <c r="A46" s="41" t="n"/>
+      <c r="B46" s="41" t="n"/>
+      <c r="C46" s="41" t="n"/>
+      <c r="D46" s="41" t="n"/>
+      <c r="E46" s="41" t="n"/>
+      <c r="F46" s="42" t="n"/>
+      <c r="G46" s="42" t="n"/>
+      <c r="H46" s="41" t="n"/>
+      <c r="I46" s="41" t="n"/>
+      <c r="J46" s="41" t="n"/>
+      <c r="K46" s="41" t="n"/>
+      <c r="L46" s="41" t="n"/>
+      <c r="M46" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="N46" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="O46" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="P46" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="Q46" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="R46" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="S46" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="T46" s="41" t="n"/>
+      <c r="U46" s="43" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="V46" s="43" t="n"/>
+      <c r="W46" s="43" t="n"/>
+      <c r="X46" s="43" t="n"/>
+      <c r="Y46" s="43" t="n"/>
+      <c r="Z46" s="43" t="n"/>
+      <c r="AA46" s="43" t="n"/>
+      <c r="AB46" s="43" t="n"/>
+      <c r="AC46" s="43" t="n"/>
+      <c r="AD46" s="43" t="n"/>
+      <c r="AE46" s="43" t="n"/>
+      <c r="AF46" s="43" t="n"/>
+      <c r="AG46" s="43" t="n"/>
+      <c r="AH46" s="43" t="n"/>
+      <c r="AI46" s="41" t="n"/>
+      <c r="AJ46" s="41" t="n"/>
+      <c r="AK46" s="41" t="n"/>
+      <c r="AL46" s="41" t="n"/>
+      <c r="AM46" s="41" t="n"/>
+      <c r="AN46" s="41" t="n"/>
+      <c r="AO46" s="41" t="n"/>
+      <c r="AP46" s="41" t="n"/>
+      <c r="AQ46" s="43" t="n"/>
+      <c r="AR46" s="43" t="n"/>
+      <c r="AS46" s="43" t="n"/>
+      <c r="AT46" s="43" t="n"/>
     </row>
     <row r="47">
-      <c r="F47" s="18" t="n"/>
-      <c r="G47" s="18" t="n"/>
+      <c r="A47" s="41" t="n"/>
+      <c r="B47" s="41" t="n"/>
+      <c r="C47" s="41" t="n"/>
+      <c r="D47" s="41" t="n"/>
+      <c r="E47" s="41" t="n"/>
+      <c r="F47" s="42" t="inlineStr">
+        <is>
+          <t>pet_icon_default.png</t>
+        </is>
+      </c>
+      <c r="G47" s="42" t="inlineStr">
+        <is>
+          <t>big_img_pet_default.png</t>
+        </is>
+      </c>
+      <c r="H47" s="41" t="n"/>
+      <c r="I47" s="41" t="n"/>
+      <c r="J47" s="41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K47" s="41" t="n"/>
+      <c r="L47" s="41" t="n"/>
+      <c r="M47" s="41" t="n"/>
+      <c r="N47" s="44" t="n"/>
+      <c r="O47" s="44" t="n"/>
+      <c r="P47" s="44" t="n"/>
+      <c r="Q47" s="44" t="n"/>
+      <c r="R47" s="44" t="n"/>
+      <c r="S47" s="44" t="n"/>
+      <c r="T47" s="44" t="n"/>
+      <c r="U47" s="41" t="n"/>
+      <c r="V47" s="43" t="n"/>
+      <c r="W47" s="43" t="n"/>
+      <c r="X47" s="43" t="n"/>
+      <c r="Y47" s="43" t="n"/>
+      <c r="Z47" s="43" t="n"/>
+      <c r="AA47" s="43" t="n"/>
+      <c r="AB47" s="43" t="n"/>
+      <c r="AC47" s="43" t="n"/>
+      <c r="AD47" s="43" t="n"/>
+      <c r="AE47" s="43" t="n"/>
+      <c r="AF47" s="43" t="n"/>
+      <c r="AG47" s="43" t="n"/>
+      <c r="AH47" s="43" t="n"/>
+      <c r="AI47" s="44" t="n"/>
+      <c r="AJ47" s="44" t="n"/>
+      <c r="AK47" s="44" t="n"/>
+      <c r="AL47" s="44" t="n"/>
+      <c r="AM47" s="44" t="n"/>
+      <c r="AN47" s="44" t="n"/>
+      <c r="AO47" s="44" t="n"/>
+      <c r="AP47" s="44" t="n"/>
+      <c r="AQ47" s="41" t="n"/>
+      <c r="AR47" s="43" t="n"/>
+      <c r="AS47" s="43" t="n"/>
+      <c r="AT47" s="43" t="n"/>
     </row>
     <row r="48">
       <c r="F48" s="18" t="n"/>

--- a/resources/pet/pet.xlsx
+++ b/resources/pet/pet.xlsx
@@ -1213,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT73"/>
+  <dimension ref="A1:AT70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -7593,80 +7593,84 @@
       </c>
     </row>
     <row r="45" customFormat="1" s="30">
-      <c r="A45" s="23" t="n">
-        <v>3066</v>
-      </c>
-      <c r="B45" s="24" t="n"/>
-      <c r="C45" s="25" t="inlineStr">
-        <is>
-          <t>九尾天狐</t>
-        </is>
-      </c>
-      <c r="D45" s="26" t="n">
-        <v>1070</v>
-      </c>
-      <c r="E45" s="26" t="n"/>
-      <c r="F45" s="27" t="n"/>
-      <c r="G45" s="27" t="n"/>
-      <c r="H45" s="24" t="n"/>
-      <c r="I45" s="24" t="n">
-        <v>3</v>
-      </c>
-      <c r="J45" s="24" t="inlineStr">
-        <is>
-          <t>fire</t>
-        </is>
-      </c>
-      <c r="K45" s="24" t="n">
-        <v>28999</v>
-      </c>
-      <c r="L45" s="24" t="n">
-        <v>60</v>
-      </c>
-      <c r="M45" s="27" t="n"/>
-      <c r="N45" s="28" t="n">
-        <v>6000</v>
-      </c>
-      <c r="O45" s="28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="P45" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Q45" s="28" t="n">
-        <v>1500</v>
-      </c>
-      <c r="R45" s="28" t="n">
-        <v>1500</v>
-      </c>
-      <c r="S45" s="28" t="n"/>
-      <c r="T45" s="28" t="n"/>
-      <c r="U45" s="28" t="n"/>
-      <c r="V45" s="28" t="n"/>
-      <c r="W45" s="28" t="n"/>
-      <c r="X45" s="28" t="n"/>
-      <c r="Y45" s="28" t="n"/>
-      <c r="Z45" s="28" t="n"/>
-      <c r="AA45" s="28" t="n"/>
-      <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="28" t="n"/>
-      <c r="AD45" s="28" t="n"/>
-      <c r="AE45" s="29" t="n"/>
-      <c r="AF45" s="29" t="n"/>
-      <c r="AG45" s="29" t="n"/>
-      <c r="AH45" s="29" t="n"/>
-      <c r="AI45" s="28" t="n"/>
-      <c r="AJ45" s="28" t="n"/>
-      <c r="AK45" s="28" t="n"/>
-      <c r="AL45" s="28" t="n"/>
-      <c r="AM45" s="28" t="n"/>
-      <c r="AN45" s="28" t="n"/>
-      <c r="AO45" s="28" t="n"/>
-      <c r="AP45" s="28" t="n"/>
-      <c r="AQ45" s="28" t="n"/>
-      <c r="AR45" s="28" t="n"/>
-      <c r="AS45" s="28" t="n"/>
-      <c r="AT45" s="28" t="n"/>
+      <c r="A45" s="41" t="n"/>
+      <c r="B45" s="41" t="n"/>
+      <c r="C45" s="41" t="n"/>
+      <c r="D45" s="41" t="n"/>
+      <c r="E45" s="41" t="n"/>
+      <c r="F45" s="42" t="n"/>
+      <c r="G45" s="42" t="n"/>
+      <c r="H45" s="41" t="n"/>
+      <c r="I45" s="41" t="n"/>
+      <c r="J45" s="41" t="n"/>
+      <c r="K45" s="41" t="n"/>
+      <c r="L45" s="41" t="n"/>
+      <c r="M45" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="N45" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="O45" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="P45" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="Q45" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="R45" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="S45" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="T45" s="41" t="n"/>
+      <c r="U45" s="43" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="V45" s="43" t="n"/>
+      <c r="W45" s="43" t="n"/>
+      <c r="X45" s="43" t="n"/>
+      <c r="Y45" s="43" t="n"/>
+      <c r="Z45" s="43" t="n"/>
+      <c r="AA45" s="43" t="n"/>
+      <c r="AB45" s="43" t="n"/>
+      <c r="AC45" s="43" t="n"/>
+      <c r="AD45" s="43" t="n"/>
+      <c r="AE45" s="43" t="n"/>
+      <c r="AF45" s="43" t="n"/>
+      <c r="AG45" s="43" t="n"/>
+      <c r="AH45" s="43" t="n"/>
+      <c r="AI45" s="41" t="n"/>
+      <c r="AJ45" s="41" t="n"/>
+      <c r="AK45" s="41" t="n"/>
+      <c r="AL45" s="41" t="n"/>
+      <c r="AM45" s="41" t="n"/>
+      <c r="AN45" s="41" t="n"/>
+      <c r="AO45" s="41" t="n"/>
+      <c r="AP45" s="41" t="n"/>
+      <c r="AQ45" s="43" t="n"/>
+      <c r="AR45" s="43" t="n"/>
+      <c r="AS45" s="43" t="n"/>
+      <c r="AT45" s="43" t="n"/>
     </row>
     <row r="46" customFormat="1" s="30">
       <c r="A46" s="41" t="n"/>
@@ -7674,54 +7678,34 @@
       <c r="C46" s="41" t="n"/>
       <c r="D46" s="41" t="n"/>
       <c r="E46" s="41" t="n"/>
-      <c r="F46" s="42" t="n"/>
-      <c r="G46" s="42" t="n"/>
+      <c r="F46" s="42" t="inlineStr">
+        <is>
+          <t>pet_icon_default.png</t>
+        </is>
+      </c>
+      <c r="G46" s="42" t="inlineStr">
+        <is>
+          <t>big_img_pet_default.png</t>
+        </is>
+      </c>
       <c r="H46" s="41" t="n"/>
       <c r="I46" s="41" t="n"/>
-      <c r="J46" s="41" t="n"/>
+      <c r="J46" s="41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
       <c r="K46" s="41" t="n"/>
       <c r="L46" s="41" t="n"/>
-      <c r="M46" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="N46" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="O46" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="P46" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="Q46" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="R46" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="S46" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="T46" s="41" t="n"/>
-      <c r="U46" s="43" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
+      <c r="M46" s="41" t="n"/>
+      <c r="N46" s="44" t="n"/>
+      <c r="O46" s="44" t="n"/>
+      <c r="P46" s="44" t="n"/>
+      <c r="Q46" s="44" t="n"/>
+      <c r="R46" s="44" t="n"/>
+      <c r="S46" s="44" t="n"/>
+      <c r="T46" s="44" t="n"/>
+      <c r="U46" s="41" t="n"/>
       <c r="V46" s="43" t="n"/>
       <c r="W46" s="43" t="n"/>
       <c r="X46" s="43" t="n"/>
@@ -7735,78 +7719,22 @@
       <c r="AF46" s="43" t="n"/>
       <c r="AG46" s="43" t="n"/>
       <c r="AH46" s="43" t="n"/>
-      <c r="AI46" s="41" t="n"/>
-      <c r="AJ46" s="41" t="n"/>
-      <c r="AK46" s="41" t="n"/>
-      <c r="AL46" s="41" t="n"/>
-      <c r="AM46" s="41" t="n"/>
-      <c r="AN46" s="41" t="n"/>
-      <c r="AO46" s="41" t="n"/>
-      <c r="AP46" s="41" t="n"/>
-      <c r="AQ46" s="43" t="n"/>
+      <c r="AI46" s="44" t="n"/>
+      <c r="AJ46" s="44" t="n"/>
+      <c r="AK46" s="44" t="n"/>
+      <c r="AL46" s="44" t="n"/>
+      <c r="AM46" s="44" t="n"/>
+      <c r="AN46" s="44" t="n"/>
+      <c r="AO46" s="44" t="n"/>
+      <c r="AP46" s="44" t="n"/>
+      <c r="AQ46" s="41" t="n"/>
       <c r="AR46" s="43" t="n"/>
       <c r="AS46" s="43" t="n"/>
       <c r="AT46" s="43" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="41" t="n"/>
-      <c r="B47" s="41" t="n"/>
-      <c r="C47" s="41" t="n"/>
-      <c r="D47" s="41" t="n"/>
-      <c r="E47" s="41" t="n"/>
-      <c r="F47" s="42" t="inlineStr">
-        <is>
-          <t>pet_icon_default.png</t>
-        </is>
-      </c>
-      <c r="G47" s="42" t="inlineStr">
-        <is>
-          <t>big_img_pet_default.png</t>
-        </is>
-      </c>
-      <c r="H47" s="41" t="n"/>
-      <c r="I47" s="41" t="n"/>
-      <c r="J47" s="41" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K47" s="41" t="n"/>
-      <c r="L47" s="41" t="n"/>
-      <c r="M47" s="41" t="n"/>
-      <c r="N47" s="44" t="n"/>
-      <c r="O47" s="44" t="n"/>
-      <c r="P47" s="44" t="n"/>
-      <c r="Q47" s="44" t="n"/>
-      <c r="R47" s="44" t="n"/>
-      <c r="S47" s="44" t="n"/>
-      <c r="T47" s="44" t="n"/>
-      <c r="U47" s="41" t="n"/>
-      <c r="V47" s="43" t="n"/>
-      <c r="W47" s="43" t="n"/>
-      <c r="X47" s="43" t="n"/>
-      <c r="Y47" s="43" t="n"/>
-      <c r="Z47" s="43" t="n"/>
-      <c r="AA47" s="43" t="n"/>
-      <c r="AB47" s="43" t="n"/>
-      <c r="AC47" s="43" t="n"/>
-      <c r="AD47" s="43" t="n"/>
-      <c r="AE47" s="43" t="n"/>
-      <c r="AF47" s="43" t="n"/>
-      <c r="AG47" s="43" t="n"/>
-      <c r="AH47" s="43" t="n"/>
-      <c r="AI47" s="44" t="n"/>
-      <c r="AJ47" s="44" t="n"/>
-      <c r="AK47" s="44" t="n"/>
-      <c r="AL47" s="44" t="n"/>
-      <c r="AM47" s="44" t="n"/>
-      <c r="AN47" s="44" t="n"/>
-      <c r="AO47" s="44" t="n"/>
-      <c r="AP47" s="44" t="n"/>
-      <c r="AQ47" s="41" t="n"/>
-      <c r="AR47" s="43" t="n"/>
-      <c r="AS47" s="43" t="n"/>
-      <c r="AT47" s="43" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
     </row>
     <row r="48">
       <c r="F48" s="18" t="n"/>
@@ -7900,18 +7828,6 @@
       <c r="F70" s="18" t="n"/>
       <c r="G70" s="18" t="n"/>
     </row>
-    <row r="71">
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-    </row>
-    <row r="72">
-      <c r="F72" s="18" t="n"/>
-      <c r="G72" s="18" t="n"/>
-    </row>
-    <row r="73">
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A10 A47:A1048576">
     <cfRule type="duplicateValues" priority="1982" dxfId="0"/>

--- a/resources/pet/pet.xlsx
+++ b/resources/pet/pet.xlsx
@@ -1213,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT70"/>
+  <dimension ref="A1:AT73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="9" min="1" max="1"/>
@@ -7593,110 +7593,108 @@
       </c>
     </row>
     <row r="45" customFormat="1" s="30">
-      <c r="A45" s="41" t="n"/>
-      <c r="B45" s="41" t="n"/>
-      <c r="C45" s="41" t="n"/>
-      <c r="D45" s="41" t="n"/>
-      <c r="E45" s="41" t="n"/>
-      <c r="F45" s="42" t="n"/>
-      <c r="G45" s="42" t="n"/>
-      <c r="H45" s="41" t="n"/>
-      <c r="I45" s="41" t="n"/>
-      <c r="J45" s="41" t="n"/>
-      <c r="K45" s="41" t="n"/>
-      <c r="L45" s="41" t="n"/>
-      <c r="M45" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="N45" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="O45" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="P45" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="Q45" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="R45" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="S45" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="T45" s="41" t="n"/>
-      <c r="U45" s="43" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="V45" s="43" t="n"/>
-      <c r="W45" s="43" t="n"/>
-      <c r="X45" s="43" t="n"/>
-      <c r="Y45" s="43" t="n"/>
-      <c r="Z45" s="43" t="n"/>
-      <c r="AA45" s="43" t="n"/>
-      <c r="AB45" s="43" t="n"/>
-      <c r="AC45" s="43" t="n"/>
-      <c r="AD45" s="43" t="n"/>
-      <c r="AE45" s="43" t="n"/>
-      <c r="AF45" s="43" t="n"/>
-      <c r="AG45" s="43" t="n"/>
-      <c r="AH45" s="43" t="n"/>
-      <c r="AI45" s="41" t="n"/>
-      <c r="AJ45" s="41" t="n"/>
-      <c r="AK45" s="41" t="n"/>
-      <c r="AL45" s="41" t="n"/>
-      <c r="AM45" s="41" t="n"/>
-      <c r="AN45" s="41" t="n"/>
-      <c r="AO45" s="41" t="n"/>
-      <c r="AP45" s="41" t="n"/>
-      <c r="AQ45" s="43" t="n"/>
-      <c r="AR45" s="43" t="n"/>
-      <c r="AS45" s="43" t="n"/>
-      <c r="AT45" s="43" t="n"/>
+      <c r="A45" s="23" t="n">
+        <v>510001</v>
+      </c>
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="25" t="inlineStr">
+        <is>
+          <t>赤焰狐</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>1301</v>
+      </c>
+      <c r="E45" s="26" t="n"/>
+      <c r="F45" s="27" t="n"/>
+      <c r="G45" s="27" t="n"/>
+      <c r="H45" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="n">
+        <v>10001</v>
+      </c>
+      <c r="L45" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="27" t="n"/>
+      <c r="N45" s="28" t="n"/>
+      <c r="O45" s="28" t="n"/>
+      <c r="P45" s="28" t="n"/>
+      <c r="Q45" s="28" t="n"/>
+      <c r="R45" s="28" t="n"/>
+      <c r="S45" s="28" t="n"/>
+      <c r="T45" s="28" t="n"/>
+      <c r="U45" s="28" t="n">
+        <v>8001</v>
+      </c>
+      <c r="V45" s="28" t="n"/>
+      <c r="W45" s="28" t="n"/>
+      <c r="X45" s="28" t="n"/>
+      <c r="Y45" s="28" t="n"/>
+      <c r="Z45" s="28" t="n"/>
+      <c r="AA45" s="28" t="n"/>
+      <c r="AB45" s="28" t="n"/>
+      <c r="AC45" s="28" t="n"/>
+      <c r="AD45" s="28" t="n"/>
+      <c r="AE45" s="29" t="n"/>
+      <c r="AF45" s="29" t="n"/>
+      <c r="AG45" s="29" t="n"/>
+      <c r="AH45" s="29" t="n"/>
+      <c r="AI45" s="28" t="n"/>
+      <c r="AJ45" s="28" t="n"/>
+      <c r="AK45" s="28" t="n"/>
+      <c r="AL45" s="28" t="n"/>
+      <c r="AM45" s="28" t="n"/>
+      <c r="AN45" s="28" t="n"/>
+      <c r="AO45" s="28" t="n"/>
+      <c r="AP45" s="28" t="n"/>
+      <c r="AQ45" s="28" t="n"/>
+      <c r="AR45" s="28" t="n"/>
+      <c r="AS45" s="28" t="n"/>
+      <c r="AT45" s="28" t="n"/>
     </row>
     <row r="46" customFormat="1" s="30">
-      <c r="A46" s="41" t="n"/>
+      <c r="A46" s="41" t="n">
+        <v>510002</v>
+      </c>
       <c r="B46" s="41" t="n"/>
-      <c r="C46" s="41" t="n"/>
-      <c r="D46" s="41" t="n"/>
+      <c r="C46" s="41" t="inlineStr">
+        <is>
+          <t>赤焰狐</t>
+        </is>
+      </c>
+      <c r="D46" s="41" t="n">
+        <v>1301</v>
+      </c>
       <c r="E46" s="41" t="n"/>
-      <c r="F46" s="42" t="inlineStr">
-        <is>
-          <t>pet_icon_default.png</t>
-        </is>
-      </c>
-      <c r="G46" s="42" t="inlineStr">
-        <is>
-          <t>big_img_pet_default.png</t>
-        </is>
-      </c>
-      <c r="H46" s="41" t="n"/>
-      <c r="I46" s="41" t="n"/>
+      <c r="F46" s="42" t="n"/>
+      <c r="G46" s="42" t="n"/>
+      <c r="H46" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" s="41" t="n">
+        <v>3</v>
+      </c>
       <c r="J46" s="41" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K46" s="41" t="n"/>
-      <c r="L46" s="41" t="n"/>
+          <t>fire</t>
+        </is>
+      </c>
+      <c r="K46" s="41" t="n">
+        <v>10003</v>
+      </c>
+      <c r="L46" s="41" t="n">
+        <v>1</v>
+      </c>
       <c r="M46" s="41" t="n"/>
       <c r="N46" s="44" t="n"/>
       <c r="O46" s="44" t="n"/>
@@ -7705,7 +7703,9 @@
       <c r="R46" s="44" t="n"/>
       <c r="S46" s="44" t="n"/>
       <c r="T46" s="44" t="n"/>
-      <c r="U46" s="41" t="n"/>
+      <c r="U46" s="41" t="n">
+        <v>8001</v>
+      </c>
       <c r="V46" s="43" t="n"/>
       <c r="W46" s="43" t="n"/>
       <c r="X46" s="43" t="n"/>
@@ -7733,12 +7733,144 @@
       <c r="AT46" s="43" t="n"/>
     </row>
     <row r="47">
-      <c r="F47" s="18" t="n"/>
-      <c r="G47" s="18" t="n"/>
+      <c r="A47" s="41" t="n"/>
+      <c r="B47" s="41" t="n"/>
+      <c r="C47" s="41" t="n"/>
+      <c r="D47" s="41" t="n"/>
+      <c r="E47" s="41" t="n"/>
+      <c r="F47" s="42" t="n"/>
+      <c r="G47" s="42" t="n"/>
+      <c r="H47" s="41" t="n"/>
+      <c r="I47" s="41" t="n"/>
+      <c r="J47" s="41" t="n"/>
+      <c r="K47" s="41" t="n"/>
+      <c r="L47" s="41" t="n"/>
+      <c r="M47" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="N47" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="O47" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="P47" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="Q47" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="R47" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="S47" s="41" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="T47" s="41" t="n"/>
+      <c r="U47" s="43" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="V47" s="43" t="n"/>
+      <c r="W47" s="43" t="n"/>
+      <c r="X47" s="43" t="n"/>
+      <c r="Y47" s="43" t="n"/>
+      <c r="Z47" s="43" t="n"/>
+      <c r="AA47" s="43" t="n"/>
+      <c r="AB47" s="43" t="n"/>
+      <c r="AC47" s="43" t="n"/>
+      <c r="AD47" s="43" t="n"/>
+      <c r="AE47" s="43" t="n"/>
+      <c r="AF47" s="43" t="n"/>
+      <c r="AG47" s="43" t="n"/>
+      <c r="AH47" s="43" t="n"/>
+      <c r="AI47" s="41" t="n"/>
+      <c r="AJ47" s="41" t="n"/>
+      <c r="AK47" s="41" t="n"/>
+      <c r="AL47" s="41" t="n"/>
+      <c r="AM47" s="41" t="n"/>
+      <c r="AN47" s="41" t="n"/>
+      <c r="AO47" s="41" t="n"/>
+      <c r="AP47" s="41" t="n"/>
+      <c r="AQ47" s="43" t="n"/>
+      <c r="AR47" s="43" t="n"/>
+      <c r="AS47" s="43" t="n"/>
+      <c r="AT47" s="43" t="n"/>
     </row>
     <row r="48">
-      <c r="F48" s="18" t="n"/>
-      <c r="G48" s="18" t="n"/>
+      <c r="A48" s="41" t="n"/>
+      <c r="B48" s="41" t="n"/>
+      <c r="C48" s="41" t="n"/>
+      <c r="D48" s="41" t="n"/>
+      <c r="E48" s="41" t="n"/>
+      <c r="F48" s="42" t="inlineStr">
+        <is>
+          <t>pet_icon_default.png</t>
+        </is>
+      </c>
+      <c r="G48" s="42" t="inlineStr">
+        <is>
+          <t>big_img_pet_default.png</t>
+        </is>
+      </c>
+      <c r="H48" s="41" t="n"/>
+      <c r="I48" s="41" t="n"/>
+      <c r="J48" s="41" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K48" s="41" t="n"/>
+      <c r="L48" s="41" t="n"/>
+      <c r="M48" s="41" t="n"/>
+      <c r="N48" s="44" t="n"/>
+      <c r="O48" s="44" t="n"/>
+      <c r="P48" s="44" t="n"/>
+      <c r="Q48" s="44" t="n"/>
+      <c r="R48" s="44" t="n"/>
+      <c r="S48" s="44" t="n"/>
+      <c r="T48" s="44" t="n"/>
+      <c r="U48" s="41" t="n"/>
+      <c r="V48" s="43" t="n"/>
+      <c r="W48" s="43" t="n"/>
+      <c r="X48" s="43" t="n"/>
+      <c r="Y48" s="43" t="n"/>
+      <c r="Z48" s="43" t="n"/>
+      <c r="AA48" s="43" t="n"/>
+      <c r="AB48" s="43" t="n"/>
+      <c r="AC48" s="43" t="n"/>
+      <c r="AD48" s="43" t="n"/>
+      <c r="AE48" s="43" t="n"/>
+      <c r="AF48" s="43" t="n"/>
+      <c r="AG48" s="43" t="n"/>
+      <c r="AH48" s="43" t="n"/>
+      <c r="AI48" s="44" t="n"/>
+      <c r="AJ48" s="44" t="n"/>
+      <c r="AK48" s="44" t="n"/>
+      <c r="AL48" s="44" t="n"/>
+      <c r="AM48" s="44" t="n"/>
+      <c r="AN48" s="44" t="n"/>
+      <c r="AO48" s="44" t="n"/>
+      <c r="AP48" s="44" t="n"/>
+      <c r="AQ48" s="41" t="n"/>
+      <c r="AR48" s="43" t="n"/>
+      <c r="AS48" s="43" t="n"/>
+      <c r="AT48" s="43" t="n"/>
     </row>
     <row r="49">
       <c r="F49" s="18" t="n"/>
@@ -7828,6 +7960,18 @@
       <c r="F70" s="18" t="n"/>
       <c r="G70" s="18" t="n"/>
     </row>
+    <row r="71">
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="18" t="n"/>
+    </row>
+    <row r="73">
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="18" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A10 A47:A1048576">
     <cfRule type="duplicateValues" priority="1982" dxfId="0"/>

--- a/resources/pet/pet.xlsx
+++ b/resources/pet/pet.xlsx
@@ -452,7 +452,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -548,39 +548,6 @@
     </xf>
     <xf numFmtId="3" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
@@ -1115,7 +1082,7 @@
           <t>生成文件</t>
         </is>
       </c>
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>SERVER</t>
         </is>
@@ -1133,7 +1100,7 @@
       <c r="E4" s="0" t="n"/>
     </row>
     <row r="5">
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>CLIENT</t>
         </is>
@@ -1187,7 +1154,7 @@
       </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" s="8">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>配置数字</t>
         </is>
@@ -1711,297 +1678,157 @@
       </c>
     </row>
     <row r="3" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="34" t="n">
-        <v>1052</v>
-      </c>
-      <c r="B3" s="35" t="n"/>
-      <c r="C3" s="36" t="inlineStr">
-        <is>
-          <t>火焰犬</t>
-        </is>
-      </c>
-      <c r="D3" s="37" t="n">
-        <v>1052</v>
-      </c>
-      <c r="E3" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="38" t="n"/>
-      <c r="G3" s="38" t="n"/>
-      <c r="H3" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" s="35" t="n"/>
-      <c r="K3" s="35" t="n"/>
-      <c r="L3" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" s="38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="39" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="O3" s="39" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="P3" s="39" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="Q3" s="39" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="R3" s="39" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="S3" s="39" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="T3" s="39" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="U3" s="39" t="n">
-        <v>8001</v>
-      </c>
-      <c r="V3" s="39" t="n">
-        <v>6556</v>
-      </c>
-      <c r="W3" s="39" t="n">
-        <v>5005</v>
-      </c>
-      <c r="X3" s="39" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Y3" s="39" t="n">
-        <v>6011</v>
-      </c>
-      <c r="Z3" s="39" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AA3" s="39" t="n">
-        <v>5040</v>
-      </c>
-      <c r="AB3" s="39" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AC3" s="39" t="n">
-        <v>5046</v>
-      </c>
-      <c r="AD3" s="39" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AE3" s="40" t="n"/>
-      <c r="AF3" s="40" t="n"/>
-      <c r="AG3" s="40" t="n"/>
-      <c r="AH3" s="40" t="n"/>
-      <c r="AI3" s="39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" s="39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" s="39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="AL3" s="39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" s="39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO3" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP3" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AQ3" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AR3" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" s="39" t="n">
-        <v>10</v>
-      </c>
+      <c r="A3" s="19" t="n"/>
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="19" t="n"/>
+      <c r="D3" s="19" t="n"/>
+      <c r="E3" s="19" t="n"/>
+      <c r="F3" s="20" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="19" t="n"/>
+      <c r="I3" s="19" t="n"/>
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="19" t="n"/>
+      <c r="L3" s="19" t="n"/>
+      <c r="M3" s="19" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="N3" s="19" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="O3" s="19" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="P3" s="19" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="Q3" s="19" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="R3" s="19" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="S3" s="19" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="T3" s="19" t="n"/>
+      <c r="U3" s="21" t="inlineStr">
+        <is>
+          <t>{required: True}</t>
+        </is>
+      </c>
+      <c r="V3" s="21" t="n"/>
+      <c r="W3" s="21" t="n"/>
+      <c r="X3" s="21" t="n"/>
+      <c r="Y3" s="21" t="n"/>
+      <c r="Z3" s="21" t="n"/>
+      <c r="AA3" s="21" t="n"/>
+      <c r="AB3" s="21" t="n"/>
+      <c r="AC3" s="21" t="n"/>
+      <c r="AD3" s="21" t="n"/>
+      <c r="AE3" s="21" t="n"/>
+      <c r="AF3" s="21" t="n"/>
+      <c r="AG3" s="21" t="n"/>
+      <c r="AH3" s="21" t="n"/>
+      <c r="AI3" s="19" t="n"/>
+      <c r="AJ3" s="19" t="n"/>
+      <c r="AK3" s="19" t="n"/>
+      <c r="AL3" s="19" t="n"/>
+      <c r="AM3" s="19" t="n"/>
+      <c r="AN3" s="19" t="n"/>
+      <c r="AO3" s="19" t="n"/>
+      <c r="AP3" s="19" t="n"/>
+      <c r="AQ3" s="21" t="n"/>
+      <c r="AR3" s="21" t="n"/>
+      <c r="AS3" s="21" t="n"/>
+      <c r="AT3" s="21" t="n"/>
     </row>
     <row r="4" ht="16.5" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="34" t="n">
-        <v>1053</v>
-      </c>
-      <c r="B4" s="35" t="n"/>
-      <c r="C4" s="36" t="inlineStr">
-        <is>
-          <t>小白鲸</t>
-        </is>
-      </c>
-      <c r="D4" s="37" t="n">
-        <v>1053</v>
-      </c>
-      <c r="E4" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="38" t="n"/>
-      <c r="G4" s="38" t="n"/>
-      <c r="H4" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" s="35" t="n"/>
-      <c r="K4" s="35" t="n"/>
-      <c r="L4" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" s="38" t="n">
-        <v>2</v>
-      </c>
-      <c r="N4" s="39" t="inlineStr">
-        <is>
-          <t>4500</t>
-        </is>
-      </c>
-      <c r="O4" s="39" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="P4" s="39" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
-      <c r="Q4" s="39" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="R4" s="39" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="S4" s="39" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="T4" s="39" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
-      <c r="U4" s="39" t="n">
-        <v>8004</v>
-      </c>
-      <c r="V4" s="39" t="n">
-        <v>5503</v>
-      </c>
-      <c r="W4" s="39" t="n">
-        <v>6553</v>
-      </c>
-      <c r="X4" s="39" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Y4" s="39" t="n">
-        <v>5029</v>
-      </c>
-      <c r="Z4" s="39" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AA4" s="39" t="n">
-        <v>5034</v>
-      </c>
-      <c r="AB4" s="39" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AC4" s="39" t="n">
-        <v>6013</v>
-      </c>
-      <c r="AD4" s="39" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AE4" s="40" t="n"/>
-      <c r="AF4" s="40" t="n"/>
-      <c r="AG4" s="40" t="n"/>
-      <c r="AH4" s="40" t="n"/>
-      <c r="AI4" s="39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" s="39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" s="39" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="AL4" s="39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" s="39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AO4" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP4" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AQ4" s="39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AR4" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" s="39" t="n">
-        <v>10</v>
-      </c>
+      <c r="A4" s="19" t="n"/>
+      <c r="B4" s="19" t="n"/>
+      <c r="C4" s="19" t="n"/>
+      <c r="D4" s="19" t="n"/>
+      <c r="E4" s="19" t="n"/>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>pet_icon_default.png</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>big_img_pet_default.png</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="n"/>
+      <c r="I4" s="19" t="n"/>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="n"/>
+      <c r="L4" s="19" t="n"/>
+      <c r="M4" s="19" t="n"/>
+      <c r="N4" s="22" t="n"/>
+      <c r="O4" s="22" t="n"/>
+      <c r="P4" s="22" t="n"/>
+      <c r="Q4" s="22" t="n"/>
+      <c r="R4" s="22" t="n"/>
+      <c r="S4" s="22" t="n"/>
+      <c r="T4" s="22" t="n"/>
+      <c r="U4" s="19" t="n"/>
+      <c r="V4" s="21" t="n"/>
+      <c r="W4" s="21" t="n"/>
+      <c r="X4" s="21" t="n"/>
+      <c r="Y4" s="21" t="n"/>
+      <c r="Z4" s="21" t="n"/>
+      <c r="AA4" s="21" t="n"/>
+      <c r="AB4" s="21" t="n"/>
+      <c r="AC4" s="21" t="n"/>
+      <c r="AD4" s="21" t="n"/>
+      <c r="AE4" s="21" t="n"/>
+      <c r="AF4" s="21" t="n"/>
+      <c r="AG4" s="21" t="n"/>
+      <c r="AH4" s="21" t="n"/>
+      <c r="AI4" s="22" t="n"/>
+      <c r="AJ4" s="22" t="n"/>
+      <c r="AK4" s="22" t="n"/>
+      <c r="AL4" s="22" t="n"/>
+      <c r="AM4" s="22" t="n"/>
+      <c r="AN4" s="22" t="n"/>
+      <c r="AO4" s="22" t="n"/>
+      <c r="AP4" s="22" t="n"/>
+      <c r="AQ4" s="19" t="n"/>
+      <c r="AR4" s="21" t="n"/>
+      <c r="AS4" s="21" t="n"/>
+      <c r="AT4" s="21" t="n"/>
     </row>
     <row r="5" customFormat="1" s="30">
       <c r="A5" s="23" t="n">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B5" s="24" t="n"/>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>木结花</t>
+          <t>火焰犬</t>
         </is>
       </c>
       <c r="D5" s="26" t="n">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E5" s="26" t="n">
         <v>0</v>
@@ -2020,69 +1847,69 @@
         <v>1</v>
       </c>
       <c r="M5" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5" s="28" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="O5" s="28" t="inlineStr">
         <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="P5" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P5" s="28" t="inlineStr">
+      <c r="Q5" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R5" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S5" s="28" t="inlineStr">
         <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="Q5" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="R5" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="S5" s="28" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
       <c r="T5" s="28" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
       <c r="U5" s="28" t="n">
-        <v>8007</v>
+        <v>8001</v>
       </c>
       <c r="V5" s="28" t="n">
-        <v>5047</v>
+        <v>6556</v>
       </c>
       <c r="W5" s="28" t="n">
-        <v>5022</v>
+        <v>5005</v>
       </c>
       <c r="X5" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y5" s="28" t="n">
-        <v>5028</v>
+        <v>6011</v>
       </c>
       <c r="Z5" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA5" s="28" t="n">
-        <v>5042</v>
+        <v>5040</v>
       </c>
       <c r="AB5" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC5" s="28" t="n">
-        <v>5026</v>
+        <v>5046</v>
       </c>
       <c r="AD5" s="28" t="n">
         <v>2500</v>
@@ -2132,19 +1959,19 @@
     </row>
     <row r="6" customFormat="1" s="30">
       <c r="A6" s="23" t="n">
-        <v>1055</v>
+        <v>2052</v>
       </c>
       <c r="B6" s="24" t="n"/>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>小顽蝠</t>
+          <t>烈焰犬</t>
         </is>
       </c>
       <c r="D6" s="26" t="n">
-        <v>1055</v>
+        <v>1052</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="27" t="n"/>
       <c r="G6" s="27" t="n"/>
@@ -2160,69 +1987,69 @@
         <v>1</v>
       </c>
       <c r="M6" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N6" s="28" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="O6" s="28" t="inlineStr">
         <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="P6" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P6" s="28" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
       <c r="Q6" s="28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="R6" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S6" s="28" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T6" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U6" s="28" t="n">
-        <v>8010</v>
+        <v>8002</v>
       </c>
       <c r="V6" s="28" t="n">
-        <v>5010</v>
+        <v>6556</v>
       </c>
       <c r="W6" s="28" t="n">
-        <v>6554</v>
+        <v>5005</v>
       </c>
       <c r="X6" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y6" s="28" t="n">
-        <v>5037</v>
+        <v>6011</v>
       </c>
       <c r="Z6" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA6" s="28" t="n">
-        <v>5038</v>
+        <v>5040</v>
       </c>
       <c r="AB6" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC6" s="28" t="n">
-        <v>5057</v>
+        <v>5046</v>
       </c>
       <c r="AD6" s="28" t="n">
         <v>2500</v>
@@ -2272,19 +2099,19 @@
     </row>
     <row r="7" customFormat="1" s="30">
       <c r="A7" s="23" t="n">
-        <v>1056</v>
+        <v>3052</v>
       </c>
       <c r="B7" s="24" t="n"/>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>慢慢龟</t>
+          <t>炽焰獒</t>
         </is>
       </c>
       <c r="D7" s="26" t="n">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" s="27" t="n"/>
       <c r="G7" s="27" t="n"/>
@@ -2300,23 +2127,23 @@
         <v>1</v>
       </c>
       <c r="M7" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" s="28" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O7" s="28" t="inlineStr">
         <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="P7" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P7" s="28" t="inlineStr">
-        <is>
-          <t>2400</t>
-        </is>
-      </c>
       <c r="Q7" s="28" t="inlineStr">
         <is>
           <t>1200</t>
@@ -2324,45 +2151,45 @@
       </c>
       <c r="R7" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S7" s="28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T7" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U7" s="28" t="n">
-        <v>8013</v>
+        <v>8003</v>
       </c>
       <c r="V7" s="28" t="n">
-        <v>5503</v>
+        <v>6556</v>
       </c>
       <c r="W7" s="28" t="n">
-        <v>5025</v>
+        <v>5005</v>
       </c>
       <c r="X7" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y7" s="28" t="n">
-        <v>6015</v>
+        <v>6011</v>
       </c>
       <c r="Z7" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA7" s="28" t="n">
-        <v>5009</v>
+        <v>5040</v>
       </c>
       <c r="AB7" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC7" s="28" t="n">
-        <v>6029</v>
+        <v>5046</v>
       </c>
       <c r="AD7" s="28" t="n">
         <v>2500</v>
@@ -2411,17 +2238,17 @@
       </c>
     </row>
     <row r="8" customFormat="1" s="30">
-      <c r="A8" s="31" t="n">
-        <v>1057</v>
+      <c r="A8" s="23" t="n">
+        <v>1053</v>
       </c>
       <c r="B8" s="24" t="n"/>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>岩岩石</t>
+          <t>小白鲸</t>
         </is>
       </c>
       <c r="D8" s="26" t="n">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="E8" s="26" t="n">
         <v>0</v>
@@ -2440,69 +2267,69 @@
         <v>1</v>
       </c>
       <c r="M8" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N8" s="28" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="O8" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P8" s="28" t="inlineStr">
         <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="Q8" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R8" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S8" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="R8" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="S8" s="28" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
       <c r="T8" s="28" t="inlineStr">
         <is>
           <t>1.15</t>
         </is>
       </c>
       <c r="U8" s="28" t="n">
-        <v>8016</v>
+        <v>8004</v>
       </c>
       <c r="V8" s="28" t="n">
-        <v>6022</v>
+        <v>5503</v>
       </c>
       <c r="W8" s="28" t="n">
-        <v>5021</v>
+        <v>6553</v>
       </c>
       <c r="X8" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y8" s="28" t="n">
-        <v>6041</v>
+        <v>5029</v>
       </c>
       <c r="Z8" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA8" s="28" t="n">
-        <v>5031</v>
+        <v>5034</v>
       </c>
       <c r="AB8" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC8" s="28" t="n">
-        <v>5019</v>
+        <v>6013</v>
       </c>
       <c r="AD8" s="28" t="n">
         <v>2500</v>
@@ -2551,20 +2378,20 @@
       </c>
     </row>
     <row r="9" customFormat="1" s="30">
-      <c r="A9" s="31" t="n">
-        <v>1058</v>
+      <c r="A9" s="23" t="n">
+        <v>2053</v>
       </c>
       <c r="B9" s="24" t="n"/>
-      <c r="C9" s="32" t="inlineStr">
-        <is>
-          <t>小编钟</t>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>大白鲸</t>
         </is>
       </c>
       <c r="D9" s="26" t="n">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="E9" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="27" t="n"/>
       <c r="G9" s="27" t="n"/>
@@ -2580,11 +2407,11 @@
         <v>1</v>
       </c>
       <c r="M9" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" s="28" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="O9" s="28" t="inlineStr">
@@ -2594,55 +2421,55 @@
       </c>
       <c r="P9" s="28" t="inlineStr">
         <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="Q9" s="28" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="R9" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S9" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="Q9" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="R9" s="28" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="S9" s="28" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
       <c r="T9" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U9" s="28" t="n">
-        <v>8019</v>
+        <v>8005</v>
       </c>
       <c r="V9" s="28" t="n">
-        <v>6027</v>
+        <v>5503</v>
       </c>
       <c r="W9" s="28" t="n">
-        <v>5020</v>
+        <v>6553</v>
       </c>
       <c r="X9" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y9" s="28" t="n">
-        <v>5022</v>
+        <v>5029</v>
       </c>
       <c r="Z9" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA9" s="28" t="n">
-        <v>5042</v>
+        <v>5034</v>
       </c>
       <c r="AB9" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC9" s="28" t="n">
-        <v>5013</v>
+        <v>6013</v>
       </c>
       <c r="AD9" s="28" t="n">
         <v>2500</v>
@@ -2691,20 +2518,20 @@
       </c>
     </row>
     <row r="10" customFormat="1" s="30">
-      <c r="A10" s="31" t="n">
-        <v>1059</v>
+      <c r="A10" s="23" t="n">
+        <v>3053</v>
       </c>
       <c r="B10" s="24" t="n"/>
-      <c r="C10" s="32" t="inlineStr">
-        <is>
-          <t>小胖墩</t>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>巨鲸</t>
         </is>
       </c>
       <c r="D10" s="26" t="n">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="E10" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F10" s="27" t="n"/>
       <c r="G10" s="27" t="n"/>
@@ -2715,76 +2542,74 @@
         <v>3</v>
       </c>
       <c r="J10" s="24" t="n"/>
-      <c r="K10" s="24" t="n">
-        <v>20004</v>
-      </c>
+      <c r="K10" s="24" t="n"/>
       <c r="L10" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M10" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N10" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O10" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P10" s="28" t="inlineStr">
         <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="Q10" s="28" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="R10" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S10" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="Q10" s="28" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="R10" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="S10" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="T10" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U10" s="28" t="n">
-        <v>8022</v>
+        <v>8006</v>
       </c>
       <c r="V10" s="28" t="n">
-        <v>6019</v>
+        <v>5503</v>
       </c>
       <c r="W10" s="28" t="n">
-        <v>5005</v>
+        <v>6553</v>
       </c>
       <c r="X10" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y10" s="28" t="n">
-        <v>5021</v>
+        <v>5029</v>
       </c>
       <c r="Z10" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA10" s="28" t="n">
-        <v>5003</v>
+        <v>5034</v>
       </c>
       <c r="AB10" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC10" s="28" t="n">
-        <v>5014</v>
+        <v>6013</v>
       </c>
       <c r="AD10" s="28" t="n">
         <v>2500</v>
@@ -2833,17 +2658,17 @@
       </c>
     </row>
     <row r="11" customFormat="1" s="30">
-      <c r="A11" s="31" t="n">
-        <v>1060</v>
+      <c r="A11" s="23" t="n">
+        <v>1054</v>
       </c>
       <c r="B11" s="24" t="n"/>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>剑灵</t>
+          <t>木结花</t>
         </is>
       </c>
       <c r="D11" s="26" t="n">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="E11" s="26" t="n">
         <v>0</v>
@@ -2862,7 +2687,7 @@
         <v>1</v>
       </c>
       <c r="M11" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N11" s="28" t="inlineStr">
         <is>
@@ -2871,7 +2696,7 @@
       </c>
       <c r="O11" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P11" s="28" t="inlineStr">
@@ -2891,7 +2716,7 @@
       </c>
       <c r="S11" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T11" s="28" t="inlineStr">
@@ -2900,31 +2725,31 @@
         </is>
       </c>
       <c r="U11" s="28" t="n">
-        <v>8025</v>
+        <v>8007</v>
       </c>
       <c r="V11" s="28" t="n">
-        <v>6044</v>
+        <v>5047</v>
       </c>
       <c r="W11" s="28" t="n">
-        <v>6004</v>
+        <v>5022</v>
       </c>
       <c r="X11" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y11" s="28" t="n">
-        <v>5001</v>
+        <v>5028</v>
       </c>
       <c r="Z11" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA11" s="28" t="n">
-        <v>5012</v>
+        <v>5042</v>
       </c>
       <c r="AB11" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC11" s="28" t="n">
-        <v>5013</v>
+        <v>5026</v>
       </c>
       <c r="AD11" s="28" t="n">
         <v>2500</v>
@@ -2973,20 +2798,20 @@
       </c>
     </row>
     <row r="12" customFormat="1" s="30">
-      <c r="A12" s="31" t="n">
-        <v>1061</v>
+      <c r="A12" s="23" t="n">
+        <v>2054</v>
       </c>
       <c r="B12" s="24" t="n"/>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>模仿玩偶</t>
+          <t>花精灵</t>
         </is>
       </c>
       <c r="D12" s="26" t="n">
-        <v>1061</v>
+        <v>1054</v>
       </c>
       <c r="E12" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="27" t="n"/>
       <c r="G12" s="27" t="n"/>
@@ -3002,11 +2827,11 @@
         <v>1</v>
       </c>
       <c r="M12" s="27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" s="28" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O12" s="28" t="inlineStr">
@@ -3016,55 +2841,55 @@
       </c>
       <c r="P12" s="28" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q12" s="28" t="inlineStr">
         <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="R12" s="28" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="R12" s="28" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
       <c r="S12" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T12" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U12" s="28" t="n">
-        <v>8028</v>
+        <v>8008</v>
       </c>
       <c r="V12" s="28" t="n">
-        <v>6007</v>
+        <v>5047</v>
       </c>
       <c r="W12" s="28" t="n">
-        <v>6551</v>
+        <v>5022</v>
       </c>
       <c r="X12" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y12" s="28" t="n">
-        <v>5006</v>
+        <v>5028</v>
       </c>
       <c r="Z12" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA12" s="28" t="n">
-        <v>5015</v>
+        <v>5042</v>
       </c>
       <c r="AB12" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC12" s="28" t="n">
-        <v>5010</v>
+        <v>5026</v>
       </c>
       <c r="AD12" s="28" t="n">
         <v>2500</v>
@@ -3113,20 +2938,20 @@
       </c>
     </row>
     <row r="13" customFormat="1" s="30">
-      <c r="A13" s="31" t="n">
-        <v>1062</v>
+      <c r="A13" s="23" t="n">
+        <v>3054</v>
       </c>
       <c r="B13" s="24" t="n"/>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>铠甲小子</t>
+          <t>蕊花仙</t>
         </is>
       </c>
       <c r="D13" s="26" t="n">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="E13" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="27" t="n"/>
       <c r="G13" s="27" t="n"/>
@@ -3142,16 +2967,16 @@
         <v>1</v>
       </c>
       <c r="M13" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N13" s="28" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O13" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P13" s="28" t="inlineStr">
@@ -3171,40 +2996,40 @@
       </c>
       <c r="S13" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T13" s="28" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U13" s="28" t="n">
-        <v>8031</v>
+        <v>8009</v>
       </c>
       <c r="V13" s="28" t="n">
-        <v>6556</v>
+        <v>5047</v>
       </c>
       <c r="W13" s="28" t="n">
-        <v>6030</v>
+        <v>5022</v>
       </c>
       <c r="X13" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y13" s="28" t="n">
-        <v>6003</v>
+        <v>5028</v>
       </c>
       <c r="Z13" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA13" s="28" t="n">
-        <v>5005</v>
+        <v>5042</v>
       </c>
       <c r="AB13" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC13" s="28" t="n">
-        <v>5019</v>
+        <v>5026</v>
       </c>
       <c r="AD13" s="28" t="n">
         <v>2500</v>
@@ -3253,17 +3078,17 @@
       </c>
     </row>
     <row r="14" customFormat="1" s="30">
-      <c r="A14" s="31" t="n">
-        <v>1063</v>
+      <c r="A14" s="23" t="n">
+        <v>1055</v>
       </c>
       <c r="B14" s="24" t="n"/>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>白泽一阶</t>
+          <t>小顽蝠</t>
         </is>
       </c>
       <c r="D14" s="26" t="n">
-        <v>1063</v>
+        <v>1055</v>
       </c>
       <c r="E14" s="26" t="n">
         <v>0</v>
@@ -3271,7 +3096,7 @@
       <c r="F14" s="27" t="n"/>
       <c r="G14" s="27" t="n"/>
       <c r="H14" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="24" t="n">
         <v>3</v>
@@ -3286,65 +3111,65 @@
       </c>
       <c r="N14" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="O14" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P14" s="28" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="Q14" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="R14" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S14" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T14" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U14" s="28" t="n">
-        <v>8034</v>
+        <v>8010</v>
       </c>
       <c r="V14" s="28" t="n">
-        <v>6007</v>
+        <v>5010</v>
       </c>
       <c r="W14" s="28" t="n">
-        <v>6009</v>
+        <v>6554</v>
       </c>
       <c r="X14" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y14" s="28" t="n">
-        <v>6010</v>
+        <v>5037</v>
       </c>
       <c r="Z14" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA14" s="28" t="n">
-        <v>5021</v>
+        <v>5038</v>
       </c>
       <c r="AB14" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC14" s="28" t="n">
-        <v>5020</v>
+        <v>5057</v>
       </c>
       <c r="AD14" s="28" t="n">
         <v>2500</v>
@@ -3393,25 +3218,25 @@
       </c>
     </row>
     <row r="15" customFormat="1" s="30">
-      <c r="A15" s="31" t="n">
-        <v>1064</v>
+      <c r="A15" s="23" t="n">
+        <v>2055</v>
       </c>
       <c r="B15" s="24" t="n"/>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>刑天一阶</t>
+          <t>吸血蝠</t>
         </is>
       </c>
       <c r="D15" s="26" t="n">
-        <v>1064</v>
+        <v>1055</v>
       </c>
       <c r="E15" s="26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="27" t="n"/>
       <c r="G15" s="27" t="n"/>
       <c r="H15" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="24" t="n">
         <v>3</v>
@@ -3422,36 +3247,36 @@
         <v>1</v>
       </c>
       <c r="M15" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="O15" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P15" s="28" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="Q15" s="28" t="inlineStr">
         <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="R15" s="28" t="inlineStr">
+        <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="R15" s="28" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
       <c r="S15" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T15" s="28" t="inlineStr">
@@ -3460,31 +3285,31 @@
         </is>
       </c>
       <c r="U15" s="28" t="n">
-        <v>8037</v>
+        <v>8011</v>
       </c>
       <c r="V15" s="28" t="n">
-        <v>6001</v>
+        <v>5010</v>
       </c>
       <c r="W15" s="28" t="n">
-        <v>6014</v>
+        <v>6554</v>
       </c>
       <c r="X15" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y15" s="28" t="n">
-        <v>6005</v>
+        <v>5037</v>
       </c>
       <c r="Z15" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA15" s="28" t="n">
-        <v>5040</v>
+        <v>5038</v>
       </c>
       <c r="AB15" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC15" s="28" t="n">
-        <v>5003</v>
+        <v>5057</v>
       </c>
       <c r="AD15" s="28" t="n">
         <v>2500</v>
@@ -3533,25 +3358,25 @@
       </c>
     </row>
     <row r="16" customFormat="1" s="30">
-      <c r="A16" s="31" t="n">
-        <v>1065</v>
+      <c r="A16" s="23" t="n">
+        <v>3055</v>
       </c>
       <c r="B16" s="24" t="n"/>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>饕餮一阶</t>
+          <t>霹雳蝠</t>
         </is>
       </c>
       <c r="D16" s="26" t="n">
-        <v>1065</v>
+        <v>1055</v>
       </c>
       <c r="E16" s="26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F16" s="27" t="n"/>
       <c r="G16" s="27" t="n"/>
       <c r="H16" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" s="24" t="n">
         <v>3</v>
@@ -3562,16 +3387,16 @@
         <v>1</v>
       </c>
       <c r="M16" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O16" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P16" s="28" t="inlineStr">
@@ -3581,50 +3406,50 @@
       </c>
       <c r="Q16" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="R16" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S16" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>900</t>
         </is>
       </c>
       <c r="T16" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U16" s="28" t="n">
-        <v>8040</v>
+        <v>8012</v>
       </c>
       <c r="V16" s="28" t="n">
-        <v>6020</v>
+        <v>5010</v>
       </c>
       <c r="W16" s="28" t="n">
-        <v>6042</v>
+        <v>6554</v>
       </c>
       <c r="X16" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y16" s="28" t="n">
-        <v>6021</v>
+        <v>5037</v>
       </c>
       <c r="Z16" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA16" s="28" t="n">
-        <v>5022</v>
+        <v>5038</v>
       </c>
       <c r="AB16" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC16" s="28" t="n">
-        <v>5047</v>
+        <v>5057</v>
       </c>
       <c r="AD16" s="28" t="n">
         <v>2500</v>
@@ -3674,19 +3499,19 @@
     </row>
     <row r="17" customFormat="1" s="30">
       <c r="A17" s="23" t="n">
-        <v>2052</v>
+        <v>1056</v>
       </c>
       <c r="B17" s="24" t="n"/>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>烈焰犬</t>
+          <t>慢慢龟</t>
         </is>
       </c>
       <c r="D17" s="26" t="n">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="E17" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" s="27" t="n"/>
       <c r="G17" s="27" t="n"/>
@@ -3702,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="M17" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N17" s="28" t="inlineStr">
         <is>
@@ -3711,12 +3536,12 @@
       </c>
       <c r="O17" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P17" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="Q17" s="28" t="inlineStr">
@@ -3726,45 +3551,45 @@
       </c>
       <c r="R17" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S17" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T17" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U17" s="28" t="n">
-        <v>8002</v>
+        <v>8013</v>
       </c>
       <c r="V17" s="28" t="n">
-        <v>6556</v>
+        <v>5503</v>
       </c>
       <c r="W17" s="28" t="n">
-        <v>5005</v>
+        <v>5025</v>
       </c>
       <c r="X17" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y17" s="28" t="n">
-        <v>6011</v>
+        <v>6015</v>
       </c>
       <c r="Z17" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA17" s="28" t="n">
-        <v>5040</v>
+        <v>5009</v>
       </c>
       <c r="AB17" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC17" s="28" t="n">
-        <v>5046</v>
+        <v>6029</v>
       </c>
       <c r="AD17" s="28" t="n">
         <v>2500</v>
@@ -3814,16 +3639,16 @@
     </row>
     <row r="18" customFormat="1" s="30">
       <c r="A18" s="23" t="n">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="B18" s="24" t="n"/>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>大白鲸</t>
+          <t>勇士龟</t>
         </is>
       </c>
       <c r="D18" s="26" t="n">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="E18" s="26" t="n">
         <v>1</v>
@@ -3846,7 +3671,7 @@
       </c>
       <c r="N18" s="28" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O18" s="28" t="inlineStr">
@@ -3866,12 +3691,12 @@
       </c>
       <c r="R18" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S18" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T18" s="28" t="inlineStr">
@@ -3880,31 +3705,31 @@
         </is>
       </c>
       <c r="U18" s="28" t="n">
-        <v>8005</v>
+        <v>8014</v>
       </c>
       <c r="V18" s="28" t="n">
         <v>5503</v>
       </c>
       <c r="W18" s="28" t="n">
-        <v>6553</v>
+        <v>5025</v>
       </c>
       <c r="X18" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y18" s="28" t="n">
-        <v>5029</v>
+        <v>6015</v>
       </c>
       <c r="Z18" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA18" s="28" t="n">
-        <v>5034</v>
+        <v>5009</v>
       </c>
       <c r="AB18" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC18" s="28" t="n">
-        <v>6013</v>
+        <v>6029</v>
       </c>
       <c r="AD18" s="28" t="n">
         <v>2500</v>
@@ -3954,19 +3779,19 @@
     </row>
     <row r="19" customFormat="1" s="30">
       <c r="A19" s="23" t="n">
-        <v>2054</v>
+        <v>3056</v>
       </c>
       <c r="B19" s="24" t="n"/>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>花精灵</t>
+          <t>千岁龟</t>
         </is>
       </c>
       <c r="D19" s="26" t="n">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="E19" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="27" t="n"/>
       <c r="G19" s="27" t="n"/>
@@ -3982,11 +3807,11 @@
         <v>1</v>
       </c>
       <c r="M19" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N19" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="O19" s="28" t="inlineStr">
@@ -3996,55 +3821,55 @@
       </c>
       <c r="P19" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="Q19" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="R19" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S19" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T19" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U19" s="28" t="n">
-        <v>8008</v>
+        <v>8015</v>
       </c>
       <c r="V19" s="28" t="n">
-        <v>5047</v>
+        <v>5503</v>
       </c>
       <c r="W19" s="28" t="n">
-        <v>5022</v>
+        <v>5025</v>
       </c>
       <c r="X19" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y19" s="28" t="n">
-        <v>5028</v>
+        <v>6015</v>
       </c>
       <c r="Z19" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA19" s="28" t="n">
-        <v>5042</v>
+        <v>5009</v>
       </c>
       <c r="AB19" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC19" s="28" t="n">
-        <v>5026</v>
+        <v>6029</v>
       </c>
       <c r="AD19" s="28" t="n">
         <v>2500</v>
@@ -4093,20 +3918,20 @@
       </c>
     </row>
     <row r="20" customFormat="1" s="30">
-      <c r="A20" s="23" t="n">
-        <v>2055</v>
+      <c r="A20" s="31" t="n">
+        <v>1057</v>
       </c>
       <c r="B20" s="24" t="n"/>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>吸血蝠</t>
+          <t>岩岩石</t>
         </is>
       </c>
       <c r="D20" s="26" t="n">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="E20" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="27" t="n"/>
       <c r="G20" s="27" t="n"/>
@@ -4122,69 +3947,69 @@
         <v>1</v>
       </c>
       <c r="M20" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N20" s="28" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4600</t>
         </is>
       </c>
       <c r="O20" s="28" t="inlineStr">
         <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="P20" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P20" s="28" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
-      </c>
       <c r="Q20" s="28" t="inlineStr">
         <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="R20" s="28" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="S20" s="28" t="inlineStr">
+        <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="R20" s="28" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="S20" s="28" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
       <c r="T20" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U20" s="28" t="n">
-        <v>8011</v>
+        <v>8016</v>
       </c>
       <c r="V20" s="28" t="n">
-        <v>5010</v>
+        <v>6022</v>
       </c>
       <c r="W20" s="28" t="n">
-        <v>6554</v>
+        <v>5021</v>
       </c>
       <c r="X20" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y20" s="28" t="n">
-        <v>5037</v>
+        <v>6041</v>
       </c>
       <c r="Z20" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA20" s="28" t="n">
-        <v>5038</v>
+        <v>5031</v>
       </c>
       <c r="AB20" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC20" s="28" t="n">
-        <v>5057</v>
+        <v>5019</v>
       </c>
       <c r="AD20" s="28" t="n">
         <v>2500</v>
@@ -4234,16 +4059,16 @@
     </row>
     <row r="21" customFormat="1" s="30">
       <c r="A21" s="23" t="n">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="B21" s="24" t="n"/>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>勇士龟</t>
+          <t>多岩小将</t>
         </is>
       </c>
       <c r="D21" s="26" t="n">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="E21" s="26" t="n">
         <v>1</v>
@@ -4262,36 +4087,36 @@
         <v>1</v>
       </c>
       <c r="M21" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="O21" s="28" t="inlineStr">
         <is>
+          <t>1550</t>
+        </is>
+      </c>
+      <c r="P21" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P21" s="28" t="inlineStr">
-        <is>
-          <t>2500</t>
-        </is>
-      </c>
       <c r="Q21" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="R21" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="S21" s="28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T21" s="28" t="inlineStr">
@@ -4300,31 +4125,31 @@
         </is>
       </c>
       <c r="U21" s="28" t="n">
-        <v>8014</v>
+        <v>8017</v>
       </c>
       <c r="V21" s="28" t="n">
-        <v>5503</v>
+        <v>6022</v>
       </c>
       <c r="W21" s="28" t="n">
-        <v>5025</v>
+        <v>5021</v>
       </c>
       <c r="X21" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y21" s="28" t="n">
-        <v>6015</v>
+        <v>6041</v>
       </c>
       <c r="Z21" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA21" s="28" t="n">
-        <v>5009</v>
+        <v>5031</v>
       </c>
       <c r="AB21" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC21" s="28" t="n">
-        <v>6029</v>
+        <v>5019</v>
       </c>
       <c r="AD21" s="28" t="n">
         <v>2500</v>
@@ -4374,19 +4199,19 @@
     </row>
     <row r="22" customFormat="1" s="30">
       <c r="A22" s="23" t="n">
-        <v>2057</v>
+        <v>3057</v>
       </c>
       <c r="B22" s="24" t="n"/>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>多岩小将</t>
+          <t>岩将军</t>
         </is>
       </c>
       <c r="D22" s="26" t="n">
         <v>1057</v>
       </c>
       <c r="E22" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="27" t="n"/>
       <c r="G22" s="27" t="n"/>
@@ -4406,12 +4231,12 @@
       </c>
       <c r="N22" s="28" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O22" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="P22" s="28" t="inlineStr">
@@ -4421,7 +4246,7 @@
       </c>
       <c r="Q22" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R22" s="28" t="inlineStr">
@@ -4436,11 +4261,11 @@
       </c>
       <c r="T22" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U22" s="28" t="n">
-        <v>8017</v>
+        <v>8018</v>
       </c>
       <c r="V22" s="28" t="n">
         <v>6022</v>
@@ -4513,20 +4338,20 @@
       </c>
     </row>
     <row r="23" customFormat="1" s="30">
-      <c r="A23" s="23" t="n">
-        <v>2058</v>
+      <c r="A23" s="31" t="n">
+        <v>1058</v>
       </c>
       <c r="B23" s="24" t="n"/>
-      <c r="C23" s="33" t="inlineStr">
-        <is>
-          <t>青铜钟偶</t>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>小编钟</t>
         </is>
       </c>
       <c r="D23" s="26" t="n">
         <v>1058</v>
       </c>
       <c r="E23" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="27" t="n"/>
       <c r="G23" s="27" t="n"/>
@@ -4546,7 +4371,7 @@
       </c>
       <c r="N23" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="O23" s="28" t="inlineStr">
@@ -4566,21 +4391,21 @@
       </c>
       <c r="R23" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S23" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T23" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U23" s="28" t="n">
-        <v>8020</v>
+        <v>8019</v>
       </c>
       <c r="V23" s="28" t="n">
         <v>6027</v>
@@ -4654,16 +4479,16 @@
     </row>
     <row r="24" customFormat="1" s="30">
       <c r="A24" s="23" t="n">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="B24" s="24" t="n"/>
       <c r="C24" s="33" t="inlineStr">
         <is>
-          <t>贪吃鬼</t>
+          <t>青铜钟偶</t>
         </is>
       </c>
       <c r="D24" s="26" t="n">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="E24" s="26" t="n">
         <v>1</v>
@@ -4682,16 +4507,16 @@
         <v>1</v>
       </c>
       <c r="M24" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N24" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O24" s="28" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P24" s="28" t="inlineStr">
@@ -4701,17 +4526,17 @@
       </c>
       <c r="Q24" s="28" t="inlineStr">
         <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R24" s="28" t="inlineStr">
+        <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="R24" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
       <c r="S24" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T24" s="28" t="inlineStr">
@@ -4720,31 +4545,31 @@
         </is>
       </c>
       <c r="U24" s="28" t="n">
-        <v>8023</v>
+        <v>8020</v>
       </c>
       <c r="V24" s="28" t="n">
-        <v>6019</v>
+        <v>6027</v>
       </c>
       <c r="W24" s="28" t="n">
-        <v>5005</v>
+        <v>5020</v>
       </c>
       <c r="X24" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y24" s="28" t="n">
-        <v>5021</v>
+        <v>5022</v>
       </c>
       <c r="Z24" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA24" s="28" t="n">
-        <v>5003</v>
+        <v>5042</v>
       </c>
       <c r="AB24" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC24" s="28" t="n">
-        <v>5014</v>
+        <v>5013</v>
       </c>
       <c r="AD24" s="28" t="n">
         <v>2500</v>
@@ -4794,19 +4619,19 @@
     </row>
     <row r="25" customFormat="1" s="30">
       <c r="A25" s="23" t="n">
-        <v>2060</v>
+        <v>3058</v>
       </c>
       <c r="B25" s="24" t="n"/>
-      <c r="C25" s="25" t="inlineStr">
-        <is>
-          <t>鬼剑</t>
+      <c r="C25" s="33" t="inlineStr">
+        <is>
+          <t>远古编钟</t>
         </is>
       </c>
       <c r="D25" s="26" t="n">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="E25" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="27" t="n"/>
       <c r="G25" s="27" t="n"/>
@@ -4822,16 +4647,16 @@
         <v>1</v>
       </c>
       <c r="M25" s="27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N25" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O25" s="28" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P25" s="28" t="inlineStr">
@@ -4846,39 +4671,39 @@
       </c>
       <c r="R25" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="S25" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="T25" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U25" s="28" t="n">
-        <v>8026</v>
+        <v>8021</v>
       </c>
       <c r="V25" s="28" t="n">
-        <v>6044</v>
+        <v>6027</v>
       </c>
       <c r="W25" s="28" t="n">
-        <v>6004</v>
+        <v>5020</v>
       </c>
       <c r="X25" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y25" s="28" t="n">
-        <v>5001</v>
+        <v>5022</v>
       </c>
       <c r="Z25" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA25" s="28" t="n">
-        <v>5012</v>
+        <v>5042</v>
       </c>
       <c r="AB25" s="28" t="n">
         <v>2500</v>
@@ -4933,20 +4758,20 @@
       </c>
     </row>
     <row r="26" customFormat="1" s="30">
-      <c r="A26" s="23" t="n">
-        <v>2061</v>
+      <c r="A26" s="31" t="n">
+        <v>1059</v>
       </c>
       <c r="B26" s="24" t="n"/>
-      <c r="C26" s="25" t="inlineStr">
-        <is>
-          <t>双影玩偶</t>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>小胖墩</t>
         </is>
       </c>
       <c r="D26" s="26" t="n">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E26" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="27" t="n"/>
       <c r="G26" s="27" t="n"/>
@@ -4957,74 +4782,76 @@
         <v>3</v>
       </c>
       <c r="J26" s="24" t="n"/>
-      <c r="K26" s="24" t="n"/>
+      <c r="K26" s="24" t="n">
+        <v>20004</v>
+      </c>
       <c r="L26" s="24" t="n">
         <v>1</v>
       </c>
       <c r="M26" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N26" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O26" s="28" t="inlineStr">
         <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="P26" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P26" s="28" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
       <c r="Q26" s="28" t="inlineStr">
         <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="R26" s="28" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="R26" s="28" t="inlineStr">
-        <is>
-          <t>1300</t>
-        </is>
-      </c>
       <c r="S26" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T26" s="28" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U26" s="28" t="n">
-        <v>8029</v>
+        <v>8022</v>
       </c>
       <c r="V26" s="28" t="n">
-        <v>6007</v>
+        <v>6019</v>
       </c>
       <c r="W26" s="28" t="n">
-        <v>6551</v>
+        <v>5005</v>
       </c>
       <c r="X26" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y26" s="28" t="n">
-        <v>5006</v>
+        <v>5021</v>
       </c>
       <c r="Z26" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA26" s="28" t="n">
-        <v>5015</v>
+        <v>5003</v>
       </c>
       <c r="AB26" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC26" s="28" t="n">
-        <v>5010</v>
+        <v>5014</v>
       </c>
       <c r="AD26" s="28" t="n">
         <v>2500</v>
@@ -5074,16 +4901,16 @@
     </row>
     <row r="27" customFormat="1" s="30">
       <c r="A27" s="23" t="n">
-        <v>2062</v>
+        <v>2059</v>
       </c>
       <c r="B27" s="24" t="n"/>
-      <c r="C27" s="25" t="inlineStr">
-        <is>
-          <t>红莲卫兵</t>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>贪吃鬼</t>
         </is>
       </c>
       <c r="D27" s="26" t="n">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="E27" s="26" t="n">
         <v>1</v>
@@ -5106,12 +4933,12 @@
       </c>
       <c r="N27" s="28" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O27" s="28" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="P27" s="28" t="inlineStr">
@@ -5131,7 +4958,7 @@
       </c>
       <c r="S27" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T27" s="28" t="inlineStr">
@@ -5140,31 +4967,31 @@
         </is>
       </c>
       <c r="U27" s="28" t="n">
-        <v>8032</v>
+        <v>8023</v>
       </c>
       <c r="V27" s="28" t="n">
-        <v>6556</v>
+        <v>6019</v>
       </c>
       <c r="W27" s="28" t="n">
-        <v>6030</v>
+        <v>5005</v>
       </c>
       <c r="X27" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y27" s="28" t="n">
-        <v>6003</v>
+        <v>5021</v>
       </c>
       <c r="Z27" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA27" s="28" t="n">
-        <v>5005</v>
+        <v>5003</v>
       </c>
       <c r="AB27" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC27" s="28" t="n">
-        <v>5019</v>
+        <v>5014</v>
       </c>
       <c r="AD27" s="28" t="n">
         <v>2500</v>
@@ -5214,24 +5041,24 @@
     </row>
     <row r="28" customFormat="1" s="30">
       <c r="A28" s="23" t="n">
-        <v>2063</v>
+        <v>3059</v>
       </c>
       <c r="B28" s="24" t="n"/>
-      <c r="C28" s="25" t="inlineStr">
-        <is>
-          <t>白泽二阶</t>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>坚韧勇士</t>
         </is>
       </c>
       <c r="D28" s="26" t="n">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="27" t="n"/>
       <c r="G28" s="27" t="n"/>
       <c r="H28" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I28" s="24" t="n">
         <v>3</v>
@@ -5242,11 +5069,11 @@
         <v>1</v>
       </c>
       <c r="M28" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N28" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="O28" s="28" t="inlineStr">
@@ -5256,22 +5083,22 @@
       </c>
       <c r="P28" s="28" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q28" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R28" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S28" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T28" s="28" t="inlineStr">
@@ -5280,31 +5107,31 @@
         </is>
       </c>
       <c r="U28" s="28" t="n">
-        <v>8035</v>
+        <v>8024</v>
       </c>
       <c r="V28" s="28" t="n">
-        <v>6007</v>
+        <v>6019</v>
       </c>
       <c r="W28" s="28" t="n">
-        <v>6009</v>
+        <v>5005</v>
       </c>
       <c r="X28" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y28" s="28" t="n">
-        <v>6010</v>
+        <v>5021</v>
       </c>
       <c r="Z28" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA28" s="28" t="n">
-        <v>5021</v>
+        <v>5003</v>
       </c>
       <c r="AB28" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC28" s="28" t="n">
-        <v>5020</v>
+        <v>5014</v>
       </c>
       <c r="AD28" s="28" t="n">
         <v>2500</v>
@@ -5353,25 +5180,25 @@
       </c>
     </row>
     <row r="29" customFormat="1" s="30">
-      <c r="A29" s="23" t="n">
-        <v>2064</v>
+      <c r="A29" s="31" t="n">
+        <v>1060</v>
       </c>
       <c r="B29" s="24" t="n"/>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>刑天二阶</t>
+          <t>剑灵</t>
         </is>
       </c>
       <c r="D29" s="26" t="n">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="E29" s="26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" s="27" t="n"/>
       <c r="G29" s="27" t="n"/>
       <c r="H29" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I29" s="24" t="n">
         <v>3</v>
@@ -5386,7 +5213,7 @@
       </c>
       <c r="N29" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="O29" s="28" t="inlineStr">
@@ -5396,55 +5223,55 @@
       </c>
       <c r="P29" s="28" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q29" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="R29" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S29" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T29" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U29" s="28" t="n">
-        <v>8038</v>
+        <v>8025</v>
       </c>
       <c r="V29" s="28" t="n">
-        <v>6001</v>
+        <v>6044</v>
       </c>
       <c r="W29" s="28" t="n">
-        <v>6014</v>
+        <v>6004</v>
       </c>
       <c r="X29" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y29" s="28" t="n">
-        <v>6005</v>
+        <v>5001</v>
       </c>
       <c r="Z29" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA29" s="28" t="n">
-        <v>5040</v>
+        <v>5012</v>
       </c>
       <c r="AB29" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC29" s="28" t="n">
-        <v>5003</v>
+        <v>5013</v>
       </c>
       <c r="AD29" s="28" t="n">
         <v>2500</v>
@@ -5494,16 +5321,16 @@
     </row>
     <row r="30" customFormat="1" s="30">
       <c r="A30" s="23" t="n">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="B30" s="24" t="n"/>
       <c r="C30" s="25" t="inlineStr">
         <is>
-          <t>饕餮二阶</t>
+          <t>鬼剑</t>
         </is>
       </c>
       <c r="D30" s="26" t="n">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="E30" s="26" t="n">
         <v>1</v>
@@ -5511,7 +5338,7 @@
       <c r="F30" s="27" t="n"/>
       <c r="G30" s="27" t="n"/>
       <c r="H30" s="24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I30" s="24" t="n">
         <v>3</v>
@@ -5522,69 +5349,69 @@
         <v>1</v>
       </c>
       <c r="M30" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N30" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O30" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="P30" s="28" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="Q30" s="28" t="inlineStr">
         <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R30" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S30" s="28" t="inlineStr">
+        <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="R30" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
-      <c r="S30" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
       <c r="T30" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U30" s="28" t="n">
-        <v>8041</v>
+        <v>8026</v>
       </c>
       <c r="V30" s="28" t="n">
-        <v>6020</v>
+        <v>6044</v>
       </c>
       <c r="W30" s="28" t="n">
-        <v>6042</v>
+        <v>6004</v>
       </c>
       <c r="X30" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y30" s="28" t="n">
-        <v>6021</v>
+        <v>5001</v>
       </c>
       <c r="Z30" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA30" s="28" t="n">
-        <v>5022</v>
+        <v>5012</v>
       </c>
       <c r="AB30" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC30" s="28" t="n">
-        <v>5047</v>
+        <v>5013</v>
       </c>
       <c r="AD30" s="28" t="n">
         <v>2500</v>
@@ -5634,16 +5461,16 @@
     </row>
     <row r="31" customFormat="1" s="30">
       <c r="A31" s="23" t="n">
-        <v>3052</v>
+        <v>3060</v>
       </c>
       <c r="B31" s="24" t="n"/>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>炽焰獒</t>
+          <t>天穹剑</t>
         </is>
       </c>
       <c r="D31" s="26" t="n">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="E31" s="26" t="n">
         <v>2</v>
@@ -5666,65 +5493,65 @@
       </c>
       <c r="N31" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O31" s="28" t="inlineStr">
         <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="P31" s="28" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="Q31" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="R31" s="28" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="S31" s="28" t="inlineStr">
+        <is>
           <t>1600</t>
         </is>
       </c>
-      <c r="P31" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="Q31" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="R31" s="28" t="inlineStr">
-        <is>
-          <t>1200</t>
-        </is>
-      </c>
-      <c r="S31" s="28" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
       <c r="T31" s="28" t="inlineStr">
         <is>
           <t>1.25</t>
         </is>
       </c>
       <c r="U31" s="28" t="n">
-        <v>8003</v>
+        <v>8027</v>
       </c>
       <c r="V31" s="28" t="n">
-        <v>6556</v>
+        <v>6044</v>
       </c>
       <c r="W31" s="28" t="n">
-        <v>5005</v>
+        <v>6004</v>
       </c>
       <c r="X31" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y31" s="28" t="n">
-        <v>6011</v>
+        <v>5001</v>
       </c>
       <c r="Z31" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA31" s="28" t="n">
-        <v>5040</v>
+        <v>5012</v>
       </c>
       <c r="AB31" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC31" s="28" t="n">
-        <v>5046</v>
+        <v>5013</v>
       </c>
       <c r="AD31" s="28" t="n">
         <v>2500</v>
@@ -5773,20 +5600,20 @@
       </c>
     </row>
     <row r="32" customFormat="1" s="30">
-      <c r="A32" s="23" t="n">
-        <v>3053</v>
+      <c r="A32" s="31" t="n">
+        <v>1061</v>
       </c>
       <c r="B32" s="24" t="n"/>
       <c r="C32" s="25" t="inlineStr">
         <is>
-          <t>巨鲸</t>
+          <t>模仿玩偶</t>
         </is>
       </c>
       <c r="D32" s="26" t="n">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F32" s="27" t="n"/>
       <c r="G32" s="27" t="n"/>
@@ -5806,7 +5633,7 @@
       </c>
       <c r="N32" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="O32" s="28" t="inlineStr">
@@ -5821,50 +5648,50 @@
       </c>
       <c r="Q32" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="R32" s="28" t="inlineStr">
         <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="S32" s="28" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="S32" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="T32" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U32" s="28" t="n">
-        <v>8006</v>
+        <v>8028</v>
       </c>
       <c r="V32" s="28" t="n">
-        <v>5503</v>
+        <v>6007</v>
       </c>
       <c r="W32" s="28" t="n">
-        <v>6553</v>
+        <v>6551</v>
       </c>
       <c r="X32" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y32" s="28" t="n">
-        <v>5029</v>
+        <v>5006</v>
       </c>
       <c r="Z32" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA32" s="28" t="n">
-        <v>5034</v>
+        <v>5015</v>
       </c>
       <c r="AB32" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC32" s="28" t="n">
-        <v>6013</v>
+        <v>5010</v>
       </c>
       <c r="AD32" s="28" t="n">
         <v>2500</v>
@@ -5914,19 +5741,19 @@
     </row>
     <row r="33" customFormat="1" s="30">
       <c r="A33" s="23" t="n">
-        <v>3054</v>
+        <v>2061</v>
       </c>
       <c r="B33" s="24" t="n"/>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>蕊花仙</t>
+          <t>双影玩偶</t>
         </is>
       </c>
       <c r="D33" s="26" t="n">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="E33" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" s="27" t="n"/>
       <c r="G33" s="27" t="n"/>
@@ -5942,11 +5769,11 @@
         <v>1</v>
       </c>
       <c r="M33" s="27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="O33" s="28" t="inlineStr">
@@ -5956,55 +5783,55 @@
       </c>
       <c r="P33" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="Q33" s="28" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="R33" s="28" t="inlineStr">
         <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="S33" s="28" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="S33" s="28" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
       <c r="T33" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U33" s="28" t="n">
-        <v>8009</v>
+        <v>8029</v>
       </c>
       <c r="V33" s="28" t="n">
-        <v>5047</v>
+        <v>6007</v>
       </c>
       <c r="W33" s="28" t="n">
-        <v>5022</v>
+        <v>6551</v>
       </c>
       <c r="X33" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y33" s="28" t="n">
-        <v>5028</v>
+        <v>5006</v>
       </c>
       <c r="Z33" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA33" s="28" t="n">
-        <v>5042</v>
+        <v>5015</v>
       </c>
       <c r="AB33" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC33" s="28" t="n">
-        <v>5026</v>
+        <v>5010</v>
       </c>
       <c r="AD33" s="28" t="n">
         <v>2500</v>
@@ -6054,16 +5881,16 @@
     </row>
     <row r="34" customFormat="1" s="30">
       <c r="A34" s="23" t="n">
-        <v>3055</v>
+        <v>3061</v>
       </c>
       <c r="B34" s="24" t="n"/>
       <c r="C34" s="25" t="inlineStr">
         <is>
-          <t>霹雳蝠</t>
+          <t>镜面玩偶</t>
         </is>
       </c>
       <c r="D34" s="26" t="n">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="E34" s="26" t="n">
         <v>2</v>
@@ -6086,7 +5913,7 @@
       </c>
       <c r="N34" s="28" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="O34" s="28" t="inlineStr">
@@ -6096,22 +5923,22 @@
       </c>
       <c r="P34" s="28" t="inlineStr">
         <is>
-          <t>2700</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="Q34" s="28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="R34" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="S34" s="28" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="T34" s="28" t="inlineStr">
@@ -6120,31 +5947,31 @@
         </is>
       </c>
       <c r="U34" s="28" t="n">
-        <v>8012</v>
+        <v>8030</v>
       </c>
       <c r="V34" s="28" t="n">
+        <v>6007</v>
+      </c>
+      <c r="W34" s="28" t="n">
+        <v>6551</v>
+      </c>
+      <c r="X34" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Y34" s="28" t="n">
+        <v>5006</v>
+      </c>
+      <c r="Z34" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AA34" s="28" t="n">
+        <v>5015</v>
+      </c>
+      <c r="AB34" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AC34" s="28" t="n">
         <v>5010</v>
-      </c>
-      <c r="W34" s="28" t="n">
-        <v>6554</v>
-      </c>
-      <c r="X34" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="Y34" s="28" t="n">
-        <v>5037</v>
-      </c>
-      <c r="Z34" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AA34" s="28" t="n">
-        <v>5038</v>
-      </c>
-      <c r="AB34" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AC34" s="28" t="n">
-        <v>5057</v>
       </c>
       <c r="AD34" s="28" t="n">
         <v>2500</v>
@@ -6193,20 +6020,20 @@
       </c>
     </row>
     <row r="35" customFormat="1" s="30">
-      <c r="A35" s="23" t="n">
-        <v>3056</v>
+      <c r="A35" s="31" t="n">
+        <v>1062</v>
       </c>
       <c r="B35" s="24" t="n"/>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>千岁龟</t>
+          <t>铠甲小子</t>
         </is>
       </c>
       <c r="D35" s="26" t="n">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="27" t="n"/>
       <c r="G35" s="27" t="n"/>
@@ -6222,23 +6049,23 @@
         <v>1</v>
       </c>
       <c r="M35" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" s="28" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="O35" s="28" t="inlineStr">
         <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="P35" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P35" s="28" t="inlineStr">
-        <is>
-          <t>2600</t>
-        </is>
-      </c>
       <c r="Q35" s="28" t="inlineStr">
         <is>
           <t>1400</t>
@@ -6246,45 +6073,45 @@
       </c>
       <c r="R35" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S35" s="28" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="T35" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="U35" s="28" t="n">
-        <v>8015</v>
+        <v>8031</v>
       </c>
       <c r="V35" s="28" t="n">
-        <v>5503</v>
+        <v>6556</v>
       </c>
       <c r="W35" s="28" t="n">
-        <v>5025</v>
+        <v>6030</v>
       </c>
       <c r="X35" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y35" s="28" t="n">
-        <v>6015</v>
+        <v>6003</v>
       </c>
       <c r="Z35" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA35" s="28" t="n">
-        <v>5009</v>
+        <v>5005</v>
       </c>
       <c r="AB35" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC35" s="28" t="n">
-        <v>6029</v>
+        <v>5019</v>
       </c>
       <c r="AD35" s="28" t="n">
         <v>2500</v>
@@ -6334,19 +6161,19 @@
     </row>
     <row r="36" customFormat="1" s="30">
       <c r="A36" s="23" t="n">
-        <v>3057</v>
+        <v>2062</v>
       </c>
       <c r="B36" s="24" t="n"/>
       <c r="C36" s="25" t="inlineStr">
         <is>
-          <t>岩将军</t>
+          <t>红莲卫兵</t>
         </is>
       </c>
       <c r="D36" s="26" t="n">
-        <v>1057</v>
+        <v>1062</v>
       </c>
       <c r="E36" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="27" t="n"/>
       <c r="G36" s="27" t="n"/>
@@ -6371,7 +6198,7 @@
       </c>
       <c r="O36" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="P36" s="28" t="inlineStr">
@@ -6381,44 +6208,44 @@
       </c>
       <c r="Q36" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="R36" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="S36" s="28" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T36" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U36" s="28" t="n">
-        <v>8018</v>
+        <v>8032</v>
       </c>
       <c r="V36" s="28" t="n">
-        <v>6022</v>
+        <v>6556</v>
       </c>
       <c r="W36" s="28" t="n">
-        <v>5021</v>
+        <v>6030</v>
       </c>
       <c r="X36" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y36" s="28" t="n">
-        <v>6041</v>
+        <v>6003</v>
       </c>
       <c r="Z36" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA36" s="28" t="n">
-        <v>5031</v>
+        <v>5005</v>
       </c>
       <c r="AB36" s="28" t="n">
         <v>2500</v>
@@ -6474,16 +6301,16 @@
     </row>
     <row r="37" customFormat="1" s="30">
       <c r="A37" s="23" t="n">
-        <v>3058</v>
+        <v>3062</v>
       </c>
       <c r="B37" s="24" t="n"/>
-      <c r="C37" s="33" t="inlineStr">
-        <is>
-          <t>远古编钟</t>
+      <c r="C37" s="25" t="inlineStr">
+        <is>
+          <t>苍炎骑士</t>
         </is>
       </c>
       <c r="D37" s="26" t="n">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="E37" s="26" t="n">
         <v>2</v>
@@ -6502,7 +6329,7 @@
         <v>1</v>
       </c>
       <c r="M37" s="27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N37" s="28" t="inlineStr">
         <is>
@@ -6511,27 +6338,27 @@
       </c>
       <c r="O37" s="28" t="inlineStr">
         <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="P37" s="28" t="inlineStr">
+        <is>
           <t>1000</t>
         </is>
       </c>
-      <c r="P37" s="28" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
       <c r="Q37" s="28" t="inlineStr">
         <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="R37" s="28" t="inlineStr">
+        <is>
           <t>1200</t>
         </is>
       </c>
-      <c r="R37" s="28" t="inlineStr">
-        <is>
-          <t>1600</t>
-        </is>
-      </c>
       <c r="S37" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T37" s="28" t="inlineStr">
@@ -6540,31 +6367,31 @@
         </is>
       </c>
       <c r="U37" s="28" t="n">
-        <v>8021</v>
+        <v>8033</v>
       </c>
       <c r="V37" s="28" t="n">
-        <v>6027</v>
+        <v>6556</v>
       </c>
       <c r="W37" s="28" t="n">
-        <v>5020</v>
+        <v>6030</v>
       </c>
       <c r="X37" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y37" s="28" t="n">
-        <v>5022</v>
+        <v>6003</v>
       </c>
       <c r="Z37" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA37" s="28" t="n">
-        <v>5042</v>
+        <v>5005</v>
       </c>
       <c r="AB37" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC37" s="28" t="n">
-        <v>5013</v>
+        <v>5019</v>
       </c>
       <c r="AD37" s="28" t="n">
         <v>2500</v>
@@ -6613,25 +6440,25 @@
       </c>
     </row>
     <row r="38" customFormat="1" s="30">
-      <c r="A38" s="23" t="n">
-        <v>3059</v>
+      <c r="A38" s="31" t="n">
+        <v>1063</v>
       </c>
       <c r="B38" s="24" t="n"/>
-      <c r="C38" s="32" t="inlineStr">
-        <is>
-          <t>坚韧勇士</t>
+      <c r="C38" s="25" t="inlineStr">
+        <is>
+          <t>白泽一阶</t>
         </is>
       </c>
       <c r="D38" s="26" t="n">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E38" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F38" s="27" t="n"/>
       <c r="G38" s="27" t="n"/>
       <c r="H38" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I38" s="24" t="n">
         <v>3</v>
@@ -6642,69 +6469,69 @@
         <v>1</v>
       </c>
       <c r="M38" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N38" s="28" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O38" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="P38" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="Q38" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="R38" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S38" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T38" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U38" s="28" t="n">
-        <v>8024</v>
+        <v>8034</v>
       </c>
       <c r="V38" s="28" t="n">
-        <v>6019</v>
+        <v>6007</v>
       </c>
       <c r="W38" s="28" t="n">
-        <v>5005</v>
+        <v>6009</v>
       </c>
       <c r="X38" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y38" s="28" t="n">
+        <v>6010</v>
+      </c>
+      <c r="Z38" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AA38" s="28" t="n">
         <v>5021</v>
       </c>
-      <c r="Z38" s="28" t="n">
-        <v>2500</v>
-      </c>
-      <c r="AA38" s="28" t="n">
-        <v>5003</v>
-      </c>
       <c r="AB38" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC38" s="28" t="n">
-        <v>5014</v>
+        <v>5020</v>
       </c>
       <c r="AD38" s="28" t="n">
         <v>2500</v>
@@ -6754,24 +6581,24 @@
     </row>
     <row r="39" customFormat="1" s="30">
       <c r="A39" s="23" t="n">
-        <v>3060</v>
+        <v>2063</v>
       </c>
       <c r="B39" s="24" t="n"/>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>天穹剑</t>
+          <t>白泽二阶</t>
         </is>
       </c>
       <c r="D39" s="26" t="n">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="E39" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" s="27" t="n"/>
       <c r="G39" s="27" t="n"/>
       <c r="H39" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="24" t="n">
         <v>3</v>
@@ -6782,7 +6609,7 @@
         <v>1</v>
       </c>
       <c r="M39" s="27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N39" s="28" t="inlineStr">
         <is>
@@ -6791,27 +6618,27 @@
       </c>
       <c r="O39" s="28" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="P39" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="Q39" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="R39" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S39" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T39" s="28" t="inlineStr">
@@ -6820,31 +6647,31 @@
         </is>
       </c>
       <c r="U39" s="28" t="n">
-        <v>8027</v>
+        <v>8035</v>
       </c>
       <c r="V39" s="28" t="n">
-        <v>6044</v>
+        <v>6007</v>
       </c>
       <c r="W39" s="28" t="n">
-        <v>6004</v>
+        <v>6009</v>
       </c>
       <c r="X39" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y39" s="28" t="n">
-        <v>5001</v>
+        <v>6010</v>
       </c>
       <c r="Z39" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA39" s="28" t="n">
-        <v>5012</v>
+        <v>5021</v>
       </c>
       <c r="AB39" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC39" s="28" t="n">
-        <v>5013</v>
+        <v>5020</v>
       </c>
       <c r="AD39" s="28" t="n">
         <v>2500</v>
@@ -6894,16 +6721,16 @@
     </row>
     <row r="40" customFormat="1" s="30">
       <c r="A40" s="23" t="n">
-        <v>3061</v>
+        <v>3063</v>
       </c>
       <c r="B40" s="24" t="n"/>
       <c r="C40" s="25" t="inlineStr">
         <is>
-          <t>镜面玩偶</t>
+          <t>白泽三阶</t>
         </is>
       </c>
       <c r="D40" s="26" t="n">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="E40" s="26" t="n">
         <v>2</v>
@@ -6911,7 +6738,7 @@
       <c r="F40" s="27" t="n"/>
       <c r="G40" s="27" t="n"/>
       <c r="H40" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I40" s="24" t="n">
         <v>3</v>
@@ -6926,65 +6753,65 @@
       </c>
       <c r="N40" s="28" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="O40" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1650</t>
         </is>
       </c>
       <c r="P40" s="28" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="Q40" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="R40" s="28" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="S40" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="T40" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="U40" s="28" t="n">
-        <v>8030</v>
+        <v>8036</v>
       </c>
       <c r="V40" s="28" t="n">
         <v>6007</v>
       </c>
       <c r="W40" s="28" t="n">
-        <v>6551</v>
+        <v>6009</v>
       </c>
       <c r="X40" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y40" s="28" t="n">
-        <v>5006</v>
+        <v>6010</v>
       </c>
       <c r="Z40" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA40" s="28" t="n">
-        <v>5015</v>
+        <v>5021</v>
       </c>
       <c r="AB40" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC40" s="28" t="n">
-        <v>5010</v>
+        <v>5020</v>
       </c>
       <c r="AD40" s="28" t="n">
         <v>2500</v>
@@ -7033,25 +6860,25 @@
       </c>
     </row>
     <row r="41" customFormat="1" s="30">
-      <c r="A41" s="23" t="n">
-        <v>3062</v>
+      <c r="A41" s="31" t="n">
+        <v>1064</v>
       </c>
       <c r="B41" s="24" t="n"/>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>苍炎骑士</t>
+          <t>刑天一阶</t>
         </is>
       </c>
       <c r="D41" s="26" t="n">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="E41" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F41" s="27" t="n"/>
       <c r="G41" s="27" t="n"/>
       <c r="H41" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" s="24" t="n">
         <v>3</v>
@@ -7066,65 +6893,65 @@
       </c>
       <c r="N41" s="28" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O41" s="28" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="P41" s="28" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="Q41" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="R41" s="28" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S41" s="28" t="inlineStr">
         <is>
-          <t>1500</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T41" s="28" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U41" s="28" t="n">
-        <v>8033</v>
+        <v>8037</v>
       </c>
       <c r="V41" s="28" t="n">
-        <v>6556</v>
+        <v>6001</v>
       </c>
       <c r="W41" s="28" t="n">
-        <v>6030</v>
+        <v>6014</v>
       </c>
       <c r="X41" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y41" s="28" t="n">
-        <v>6003</v>
+        <v>6005</v>
       </c>
       <c r="Z41" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA41" s="28" t="n">
-        <v>5005</v>
+        <v>5040</v>
       </c>
       <c r="AB41" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC41" s="28" t="n">
-        <v>5019</v>
+        <v>5003</v>
       </c>
       <c r="AD41" s="28" t="n">
         <v>2500</v>
@@ -7174,19 +7001,19 @@
     </row>
     <row r="42" customFormat="1" s="30">
       <c r="A42" s="23" t="n">
-        <v>3063</v>
+        <v>2064</v>
       </c>
       <c r="B42" s="24" t="n"/>
       <c r="C42" s="25" t="inlineStr">
         <is>
-          <t>白泽三阶</t>
+          <t>刑天二阶</t>
         </is>
       </c>
       <c r="D42" s="26" t="n">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E42" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" s="27" t="n"/>
       <c r="G42" s="27" t="n"/>
@@ -7202,69 +7029,69 @@
         <v>1</v>
       </c>
       <c r="M42" s="27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N42" s="28" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="O42" s="28" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="P42" s="28" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="Q42" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="R42" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="S42" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1500</t>
         </is>
       </c>
       <c r="T42" s="28" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="U42" s="28" t="n">
-        <v>8036</v>
+        <v>8038</v>
       </c>
       <c r="V42" s="28" t="n">
-        <v>6007</v>
+        <v>6001</v>
       </c>
       <c r="W42" s="28" t="n">
-        <v>6009</v>
+        <v>6014</v>
       </c>
       <c r="X42" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="Y42" s="28" t="n">
-        <v>6010</v>
+        <v>6005</v>
       </c>
       <c r="Z42" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AA42" s="28" t="n">
-        <v>5021</v>
+        <v>5040</v>
       </c>
       <c r="AB42" s="28" t="n">
         <v>2500</v>
       </c>
       <c r="AC42" s="28" t="n">
-        <v>5020</v>
+        <v>5003</v>
       </c>
       <c r="AD42" s="28" t="n">
         <v>2500</v>
@@ -7453,20 +7280,20 @@
       </c>
     </row>
     <row r="44" customFormat="1" s="30">
-      <c r="A44" s="23" t="n">
-        <v>3065</v>
+      <c r="A44" s="31" t="n">
+        <v>1065</v>
       </c>
       <c r="B44" s="24" t="n"/>
       <c r="C44" s="25" t="inlineStr">
         <is>
-          <t>饕餮三阶</t>
+          <t>饕餮一阶</t>
         </is>
       </c>
       <c r="D44" s="26" t="n">
         <v>1065</v>
       </c>
       <c r="E44" s="26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" s="27" t="n"/>
       <c r="G44" s="27" t="n"/>
@@ -7486,41 +7313,41 @@
       </c>
       <c r="N44" s="28" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="O44" s="28" t="inlineStr">
         <is>
-          <t>1650</t>
+          <t>1550</t>
         </is>
       </c>
       <c r="P44" s="28" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="Q44" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="R44" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="S44" s="28" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="T44" s="28" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="U44" s="28" t="n">
-        <v>8042</v>
+        <v>8040</v>
       </c>
       <c r="V44" s="28" t="n">
         <v>6020</v>
@@ -7594,283 +7421,291 @@
     </row>
     <row r="45" customFormat="1" s="30">
       <c r="A45" s="23" t="n">
-        <v>510001</v>
+        <v>2065</v>
       </c>
       <c r="B45" s="24" t="n"/>
       <c r="C45" s="25" t="inlineStr">
         <is>
-          <t>赤焰狐</t>
+          <t>饕餮二阶</t>
         </is>
       </c>
       <c r="D45" s="26" t="n">
-        <v>1301</v>
-      </c>
-      <c r="E45" s="26" t="n"/>
+        <v>1065</v>
+      </c>
+      <c r="E45" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="F45" s="27" t="n"/>
       <c r="G45" s="27" t="n"/>
       <c r="H45" s="24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J45" s="24" t="inlineStr">
-        <is>
-          <t>fire</t>
-        </is>
-      </c>
-      <c r="K45" s="24" t="n">
-        <v>10001</v>
-      </c>
+      <c r="J45" s="24" t="n"/>
+      <c r="K45" s="24" t="n"/>
       <c r="L45" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="M45" s="27" t="n"/>
-      <c r="N45" s="28" t="n"/>
-      <c r="O45" s="28" t="n"/>
-      <c r="P45" s="28" t="n"/>
-      <c r="Q45" s="28" t="n"/>
-      <c r="R45" s="28" t="n"/>
-      <c r="S45" s="28" t="n"/>
-      <c r="T45" s="28" t="n"/>
+      <c r="M45" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" s="28" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="O45" s="28" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="P45" s="28" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="Q45" s="28" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="R45" s="28" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="S45" s="28" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="T45" s="28" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
       <c r="U45" s="28" t="n">
-        <v>8001</v>
-      </c>
-      <c r="V45" s="28" t="n"/>
-      <c r="W45" s="28" t="n"/>
-      <c r="X45" s="28" t="n"/>
-      <c r="Y45" s="28" t="n"/>
-      <c r="Z45" s="28" t="n"/>
-      <c r="AA45" s="28" t="n"/>
-      <c r="AB45" s="28" t="n"/>
-      <c r="AC45" s="28" t="n"/>
-      <c r="AD45" s="28" t="n"/>
+        <v>8041</v>
+      </c>
+      <c r="V45" s="28" t="n">
+        <v>6020</v>
+      </c>
+      <c r="W45" s="28" t="n">
+        <v>6042</v>
+      </c>
+      <c r="X45" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Y45" s="28" t="n">
+        <v>6021</v>
+      </c>
+      <c r="Z45" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AA45" s="28" t="n">
+        <v>5022</v>
+      </c>
+      <c r="AB45" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AC45" s="28" t="n">
+        <v>5047</v>
+      </c>
+      <c r="AD45" s="28" t="n">
+        <v>2500</v>
+      </c>
       <c r="AE45" s="29" t="n"/>
       <c r="AF45" s="29" t="n"/>
       <c r="AG45" s="29" t="n"/>
       <c r="AH45" s="29" t="n"/>
-      <c r="AI45" s="28" t="n"/>
-      <c r="AJ45" s="28" t="n"/>
-      <c r="AK45" s="28" t="n"/>
-      <c r="AL45" s="28" t="n"/>
-      <c r="AM45" s="28" t="n"/>
-      <c r="AN45" s="28" t="n"/>
-      <c r="AO45" s="28" t="n"/>
-      <c r="AP45" s="28" t="n"/>
-      <c r="AQ45" s="28" t="n"/>
-      <c r="AR45" s="28" t="n"/>
-      <c r="AS45" s="28" t="n"/>
-      <c r="AT45" s="28" t="n"/>
+      <c r="AI45" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK45" s="28" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AL45" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM45" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO45" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP45" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ45" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR45" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" s="28" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="46" customFormat="1" s="30">
-      <c r="A46" s="41" t="n">
-        <v>510002</v>
-      </c>
-      <c r="B46" s="41" t="n"/>
-      <c r="C46" s="41" t="inlineStr">
-        <is>
-          <t>赤焰狐</t>
-        </is>
-      </c>
-      <c r="D46" s="41" t="n">
-        <v>1301</v>
-      </c>
-      <c r="E46" s="41" t="n"/>
-      <c r="F46" s="42" t="n"/>
-      <c r="G46" s="42" t="n"/>
-      <c r="H46" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="41" t="n">
+      <c r="A46" s="23" t="n">
+        <v>3065</v>
+      </c>
+      <c r="B46" s="24" t="n"/>
+      <c r="C46" s="25" t="inlineStr">
+        <is>
+          <t>饕餮三阶</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="n">
+        <v>1065</v>
+      </c>
+      <c r="E46" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="27" t="n"/>
+      <c r="G46" s="27" t="n"/>
+      <c r="H46" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="J46" s="41" t="inlineStr">
-        <is>
-          <t>fire</t>
-        </is>
-      </c>
-      <c r="K46" s="41" t="n">
-        <v>10003</v>
-      </c>
-      <c r="L46" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="41" t="n"/>
-      <c r="N46" s="44" t="n"/>
-      <c r="O46" s="44" t="n"/>
-      <c r="P46" s="44" t="n"/>
-      <c r="Q46" s="44" t="n"/>
-      <c r="R46" s="44" t="n"/>
-      <c r="S46" s="44" t="n"/>
-      <c r="T46" s="44" t="n"/>
-      <c r="U46" s="41" t="n">
-        <v>8001</v>
-      </c>
-      <c r="V46" s="43" t="n"/>
-      <c r="W46" s="43" t="n"/>
-      <c r="X46" s="43" t="n"/>
-      <c r="Y46" s="43" t="n"/>
-      <c r="Z46" s="43" t="n"/>
-      <c r="AA46" s="43" t="n"/>
-      <c r="AB46" s="43" t="n"/>
-      <c r="AC46" s="43" t="n"/>
-      <c r="AD46" s="43" t="n"/>
-      <c r="AE46" s="43" t="n"/>
-      <c r="AF46" s="43" t="n"/>
-      <c r="AG46" s="43" t="n"/>
-      <c r="AH46" s="43" t="n"/>
-      <c r="AI46" s="44" t="n"/>
-      <c r="AJ46" s="44" t="n"/>
-      <c r="AK46" s="44" t="n"/>
-      <c r="AL46" s="44" t="n"/>
-      <c r="AM46" s="44" t="n"/>
-      <c r="AN46" s="44" t="n"/>
-      <c r="AO46" s="44" t="n"/>
-      <c r="AP46" s="44" t="n"/>
-      <c r="AQ46" s="41" t="n"/>
-      <c r="AR46" s="43" t="n"/>
-      <c r="AS46" s="43" t="n"/>
-      <c r="AT46" s="43" t="n"/>
+      <c r="J46" s="24" t="n"/>
+      <c r="K46" s="24" t="n"/>
+      <c r="L46" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="N46" s="28" t="inlineStr">
+        <is>
+          <t>5400</t>
+        </is>
+      </c>
+      <c r="O46" s="28" t="inlineStr">
+        <is>
+          <t>1650</t>
+        </is>
+      </c>
+      <c r="P46" s="28" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="Q46" s="28" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="R46" s="28" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="S46" s="28" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="T46" s="28" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="U46" s="28" t="n">
+        <v>8042</v>
+      </c>
+      <c r="V46" s="28" t="n">
+        <v>6020</v>
+      </c>
+      <c r="W46" s="28" t="n">
+        <v>6042</v>
+      </c>
+      <c r="X46" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="Y46" s="28" t="n">
+        <v>6021</v>
+      </c>
+      <c r="Z46" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AA46" s="28" t="n">
+        <v>5022</v>
+      </c>
+      <c r="AB46" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AC46" s="28" t="n">
+        <v>5047</v>
+      </c>
+      <c r="AD46" s="28" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AE46" s="29" t="n"/>
+      <c r="AF46" s="29" t="n"/>
+      <c r="AG46" s="29" t="n"/>
+      <c r="AH46" s="29" t="n"/>
+      <c r="AI46" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ46" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK46" s="28" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="AL46" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM46" s="28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN46" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AO46" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP46" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AQ46" s="28" t="n">
+        <v>100</v>
+      </c>
+      <c r="AR46" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" s="28" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="41" t="n"/>
-      <c r="B47" s="41" t="n"/>
-      <c r="C47" s="41" t="n"/>
-      <c r="D47" s="41" t="n"/>
-      <c r="E47" s="41" t="n"/>
-      <c r="F47" s="42" t="n"/>
-      <c r="G47" s="42" t="n"/>
-      <c r="H47" s="41" t="n"/>
-      <c r="I47" s="41" t="n"/>
-      <c r="J47" s="41" t="n"/>
-      <c r="K47" s="41" t="n"/>
-      <c r="L47" s="41" t="n"/>
-      <c r="M47" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="N47" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="O47" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="P47" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="Q47" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="R47" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="S47" s="41" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="T47" s="41" t="n"/>
-      <c r="U47" s="43" t="inlineStr">
-        <is>
-          <t>{required: True}</t>
-        </is>
-      </c>
-      <c r="V47" s="43" t="n"/>
-      <c r="W47" s="43" t="n"/>
-      <c r="X47" s="43" t="n"/>
-      <c r="Y47" s="43" t="n"/>
-      <c r="Z47" s="43" t="n"/>
-      <c r="AA47" s="43" t="n"/>
-      <c r="AB47" s="43" t="n"/>
-      <c r="AC47" s="43" t="n"/>
-      <c r="AD47" s="43" t="n"/>
-      <c r="AE47" s="43" t="n"/>
-      <c r="AF47" s="43" t="n"/>
-      <c r="AG47" s="43" t="n"/>
-      <c r="AH47" s="43" t="n"/>
-      <c r="AI47" s="41" t="n"/>
-      <c r="AJ47" s="41" t="n"/>
-      <c r="AK47" s="41" t="n"/>
-      <c r="AL47" s="41" t="n"/>
-      <c r="AM47" s="41" t="n"/>
-      <c r="AN47" s="41" t="n"/>
-      <c r="AO47" s="41" t="n"/>
-      <c r="AP47" s="41" t="n"/>
-      <c r="AQ47" s="43" t="n"/>
-      <c r="AR47" s="43" t="n"/>
-      <c r="AS47" s="43" t="n"/>
-      <c r="AT47" s="43" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="18" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="41" t="n"/>
-      <c r="B48" s="41" t="n"/>
-      <c r="C48" s="41" t="n"/>
-      <c r="D48" s="41" t="n"/>
-      <c r="E48" s="41" t="n"/>
-      <c r="F48" s="42" t="inlineStr">
-        <is>
-          <t>pet_icon_default.png</t>
-        </is>
-      </c>
-      <c r="G48" s="42" t="inlineStr">
-        <is>
-          <t>big_img_pet_default.png</t>
-        </is>
-      </c>
-      <c r="H48" s="41" t="n"/>
-      <c r="I48" s="41" t="n"/>
-      <c r="J48" s="41" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K48" s="41" t="n"/>
-      <c r="L48" s="41" t="n"/>
-      <c r="M48" s="41" t="n"/>
-      <c r="N48" s="44" t="n"/>
-      <c r="O48" s="44" t="n"/>
-      <c r="P48" s="44" t="n"/>
-      <c r="Q48" s="44" t="n"/>
-      <c r="R48" s="44" t="n"/>
-      <c r="S48" s="44" t="n"/>
-      <c r="T48" s="44" t="n"/>
-      <c r="U48" s="41" t="n"/>
-      <c r="V48" s="43" t="n"/>
-      <c r="W48" s="43" t="n"/>
-      <c r="X48" s="43" t="n"/>
-      <c r="Y48" s="43" t="n"/>
-      <c r="Z48" s="43" t="n"/>
-      <c r="AA48" s="43" t="n"/>
-      <c r="AB48" s="43" t="n"/>
-      <c r="AC48" s="43" t="n"/>
-      <c r="AD48" s="43" t="n"/>
-      <c r="AE48" s="43" t="n"/>
-      <c r="AF48" s="43" t="n"/>
-      <c r="AG48" s="43" t="n"/>
-      <c r="AH48" s="43" t="n"/>
-      <c r="AI48" s="44" t="n"/>
-      <c r="AJ48" s="44" t="n"/>
-      <c r="AK48" s="44" t="n"/>
-      <c r="AL48" s="44" t="n"/>
-      <c r="AM48" s="44" t="n"/>
-      <c r="AN48" s="44" t="n"/>
-      <c r="AO48" s="44" t="n"/>
-      <c r="AP48" s="44" t="n"/>
-      <c r="AQ48" s="41" t="n"/>
-      <c r="AR48" s="43" t="n"/>
-      <c r="AS48" s="43" t="n"/>
-      <c r="AT48" s="43" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
     </row>
     <row r="49">
       <c r="F49" s="18" t="n"/>
